--- a/Data_Komposisi_Jenis_Sampah/Data_Komposisi_Jenis_Sampah_SIPSN_KLHK_2021.xlsx
+++ b/Data_Komposisi_Jenis_Sampah/Data_Komposisi_Jenis_Sampah_SIPSN_KLHK_2021.xlsx
@@ -201,8 +201,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <cols>
     <col min="1" max="1" width="6.75" customWidth="1"/>
-    <col min="2" max="2" width="18.900000000000002" customWidth="1"/>
-    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="2" max="2" width="35.1" customWidth="1"/>
+    <col min="3" max="3" width="40.5" customWidth="1"/>
     <col min="4" max="4" width="21.6" customWidth="1"/>
     <col min="5" max="5" width="21.6" customWidth="1"/>
     <col min="6" max="6" width="22.950000000000003" customWidth="1"/>
@@ -676,6 +676,7788 @@
         <v>33.03</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B13">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C13">
+        <is>
+          <t xml:space="preserve">Kab. Deli Serdang</t>
+        </is>
+      </c>
+      <c r="D13" s="66">
+        <v>20.50</v>
+      </c>
+      <c r="E13" s="66">
+        <v>24.00</v>
+      </c>
+      <c r="F13" s="66">
+        <v>13.80</v>
+      </c>
+      <c r="G13" s="66">
+        <v>20.20</v>
+      </c>
+      <c r="H13" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="I13" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="J13" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="K13" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L13" s="66">
+        <v>5.50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B14">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C14">
+        <is>
+          <t xml:space="preserve">Kab. Simalungun</t>
+        </is>
+      </c>
+      <c r="D14" s="66">
+        <v>0.53</v>
+      </c>
+      <c r="E14" s="66">
+        <v>22.63</v>
+      </c>
+      <c r="F14" s="66">
+        <v>28.29</v>
+      </c>
+      <c r="G14" s="66">
+        <v>19.58</v>
+      </c>
+      <c r="H14" s="66">
+        <v>11.40</v>
+      </c>
+      <c r="I14" s="66">
+        <v>0.04</v>
+      </c>
+      <c r="J14" s="66">
+        <v>0.05</v>
+      </c>
+      <c r="K14" s="66">
+        <v>8.16</v>
+      </c>
+      <c r="L14" s="66">
+        <v>9.32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B15">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C15">
+        <is>
+          <t xml:space="preserve">Kab. Asahan</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C16">
+        <is>
+          <t xml:space="preserve">Kab. Labuhanbatu</t>
+        </is>
+      </c>
+      <c r="D16" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="E16" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="F16" s="66">
+        <v>11.00</v>
+      </c>
+      <c r="G16" s="66">
+        <v>30.00</v>
+      </c>
+      <c r="H16" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="I16" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="J16" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K16" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="L16" s="66">
+        <v>4.00</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B17">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C17">
+        <is>
+          <t xml:space="preserve">Kab. Toba</t>
+        </is>
+      </c>
+      <c r="D17" s="66">
+        <v>23.15</v>
+      </c>
+      <c r="E17" s="66">
+        <v>13.41</v>
+      </c>
+      <c r="F17" s="66">
+        <v>4.12</v>
+      </c>
+      <c r="G17" s="66">
+        <v>12.38</v>
+      </c>
+      <c r="H17" s="66">
+        <v>2.38</v>
+      </c>
+      <c r="I17" s="66">
+        <v>4.57</v>
+      </c>
+      <c r="J17" s="66">
+        <v>13.25</v>
+      </c>
+      <c r="K17" s="66">
+        <v>6.45</v>
+      </c>
+      <c r="L17" s="66">
+        <v>20.29</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B18">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C18">
+        <is>
+          <t xml:space="preserve">Kab. Samosir</t>
+        </is>
+      </c>
+      <c r="D18" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="E18" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="F18" s="66">
+        <v>18.00</v>
+      </c>
+      <c r="G18" s="66">
+        <v>32.00</v>
+      </c>
+      <c r="H18" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="I18" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="J18" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K18" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="L18" s="66">
+        <v>4.00</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B19">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C19">
+        <is>
+          <t xml:space="preserve">Kota Medan</t>
+        </is>
+      </c>
+      <c r="D19" s="66">
+        <v>40.00</v>
+      </c>
+      <c r="E19" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="F19" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="G19" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="H19" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="I19" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="J19" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="K19" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L19" s="66">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B20">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C20">
+        <is>
+          <t xml:space="preserve">Kota Pematangsiantar</t>
+        </is>
+      </c>
+      <c r="D20" s="66">
+        <v>45.00</v>
+      </c>
+      <c r="E20" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="F20" s="66">
+        <v>12.00</v>
+      </c>
+      <c r="G20" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="H20" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="I20" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="J20" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="K20" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="L20" s="66">
+        <v>11.00</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B21">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C21">
+        <is>
+          <t xml:space="preserve">Kota Tebing Tinggi</t>
+        </is>
+      </c>
+      <c r="D21" s="66">
+        <v>62.70</v>
+      </c>
+      <c r="E21" s="66">
+        <v>1.73</v>
+      </c>
+      <c r="F21" s="66">
+        <v>11.43</v>
+      </c>
+      <c r="G21" s="66">
+        <v>16.65</v>
+      </c>
+      <c r="H21" s="66">
+        <v>0.73</v>
+      </c>
+      <c r="I21" s="66">
+        <v>2.60</v>
+      </c>
+      <c r="J21" s="66">
+        <v>0.71</v>
+      </c>
+      <c r="K21" s="66">
+        <v>1.83</v>
+      </c>
+      <c r="L21" s="66">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B22">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C22">
+        <is>
+          <t xml:space="preserve">Kab. Pesisir Selatan</t>
+        </is>
+      </c>
+      <c r="D22" s="66">
+        <v>20.40</v>
+      </c>
+      <c r="E22" s="66">
+        <v>19.60</v>
+      </c>
+      <c r="F22" s="66">
+        <v>23.00</v>
+      </c>
+      <c r="G22" s="66">
+        <v>19.00</v>
+      </c>
+      <c r="H22" s="66">
+        <v>16.00</v>
+      </c>
+      <c r="I22" s="66">
+        <v>0.42</v>
+      </c>
+      <c r="J22" s="66">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B23">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C23">
+        <is>
+          <t xml:space="preserve">Kab. Tanah Datar</t>
+        </is>
+      </c>
+      <c r="D23" s="66">
+        <v>69.34</v>
+      </c>
+      <c r="F23" s="66">
+        <v>8.63</v>
+      </c>
+      <c r="G23" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="H23" s="66">
+        <v>2.24</v>
+      </c>
+      <c r="I23" s="66">
+        <v>1.57</v>
+      </c>
+      <c r="K23" s="66">
+        <v>3.33</v>
+      </c>
+      <c r="L23" s="66">
+        <v>8.89</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B24">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C24">
+        <is>
+          <t xml:space="preserve">Kab. Agam</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B25">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C25">
+        <is>
+          <t xml:space="preserve">Kab. Lima Puluh Kota</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B26">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C26">
+        <is>
+          <t xml:space="preserve">Kab. Pasaman</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B27">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C27">
+        <is>
+          <t xml:space="preserve">Kab. Dharmasraya</t>
+        </is>
+      </c>
+      <c r="D27" s="66">
+        <v>48.00</v>
+      </c>
+      <c r="E27" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="F27" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="G27" s="66">
+        <v>38.00</v>
+      </c>
+      <c r="H27" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="I27" s="66">
+        <v>1.00</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B28">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C28">
+        <is>
+          <t xml:space="preserve">Kab. Solok Selatan</t>
+        </is>
+      </c>
+      <c r="D28" s="66">
+        <v>34.25</v>
+      </c>
+      <c r="E28" s="66">
+        <v>0.78</v>
+      </c>
+      <c r="F28" s="66">
+        <v>16.35</v>
+      </c>
+      <c r="G28" s="66">
+        <v>25.69</v>
+      </c>
+      <c r="H28" s="66">
+        <v>0.13</v>
+      </c>
+      <c r="I28" s="66">
+        <v>0.59</v>
+      </c>
+      <c r="J28" s="66">
+        <v>0.55</v>
+      </c>
+      <c r="K28" s="66">
+        <v>2.41</v>
+      </c>
+      <c r="L28" s="66">
+        <v>19.25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B29">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C29">
+        <is>
+          <t xml:space="preserve">Kota Solok</t>
+        </is>
+      </c>
+      <c r="D29" s="66">
+        <v>45.66</v>
+      </c>
+      <c r="E29" s="66">
+        <v>11.37</v>
+      </c>
+      <c r="F29" s="66">
+        <v>10.01</v>
+      </c>
+      <c r="G29" s="66">
+        <v>22.02</v>
+      </c>
+      <c r="H29" s="66">
+        <v>0.62</v>
+      </c>
+      <c r="I29" s="66">
+        <v>0.52</v>
+      </c>
+      <c r="J29" s="66">
+        <v>0.19</v>
+      </c>
+      <c r="K29" s="66">
+        <v>1.20</v>
+      </c>
+      <c r="L29" s="66">
+        <v>8.41</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B30">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C30">
+        <is>
+          <t xml:space="preserve">Kota Sawahlunto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B31">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C31">
+        <is>
+          <t xml:space="preserve">Kota Padang Panjang</t>
+        </is>
+      </c>
+      <c r="D31" s="66">
+        <v>43.15</v>
+      </c>
+      <c r="E31" s="66">
+        <v>23.56</v>
+      </c>
+      <c r="F31" s="66">
+        <v>14.35</v>
+      </c>
+      <c r="G31" s="66">
+        <v>12.67</v>
+      </c>
+      <c r="H31" s="66">
+        <v>1.50</v>
+      </c>
+      <c r="I31" s="66">
+        <v>0.95</v>
+      </c>
+      <c r="J31" s="66">
+        <v>0.80</v>
+      </c>
+      <c r="K31" s="66">
+        <v>1.19</v>
+      </c>
+      <c r="L31" s="66">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B32">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C32">
+        <is>
+          <t xml:space="preserve">Kota Payakumbuh</t>
+        </is>
+      </c>
+      <c r="D32" s="66">
+        <v>51.62</v>
+      </c>
+      <c r="E32" s="66">
+        <v>7.43</v>
+      </c>
+      <c r="F32" s="66">
+        <v>11.42</v>
+      </c>
+      <c r="G32" s="66">
+        <v>21.54</v>
+      </c>
+      <c r="H32" s="66">
+        <v>0.65</v>
+      </c>
+      <c r="I32" s="66">
+        <v>1.56</v>
+      </c>
+      <c r="J32" s="66">
+        <v>0.57</v>
+      </c>
+      <c r="K32" s="66">
+        <v>0.87</v>
+      </c>
+      <c r="L32" s="66">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B33">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C33">
+        <is>
+          <t xml:space="preserve">Kab. Indragiri Hilir</t>
+        </is>
+      </c>
+      <c r="D33" s="66">
+        <v>65.00</v>
+      </c>
+      <c r="E33" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="F33" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="G33" s="66">
+        <v>30.00</v>
+      </c>
+      <c r="I33" s="66">
+        <v>1.00</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B34">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C34">
+        <is>
+          <t xml:space="preserve">Kab. Siak</t>
+        </is>
+      </c>
+      <c r="D34" s="66">
+        <v>39.00</v>
+      </c>
+      <c r="E34" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="F34" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="G34" s="66">
+        <v>26.00</v>
+      </c>
+      <c r="H34" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="I34" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="J34" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K34" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="L34" s="66">
+        <v>2.00</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B35">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C35">
+        <is>
+          <t xml:space="preserve">Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="D35" s="66">
+        <v>59.00</v>
+      </c>
+      <c r="E35" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="F35" s="66">
+        <v>12.00</v>
+      </c>
+      <c r="G35" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="H35" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="I35" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="J35" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="K35" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="L35" s="66">
+        <v>11.00</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B36">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C36">
+        <is>
+          <t xml:space="preserve">Kota Dumai</t>
+        </is>
+      </c>
+      <c r="D36" s="66">
+        <v>45.75</v>
+      </c>
+      <c r="E36" s="66">
+        <v>7.25</v>
+      </c>
+      <c r="F36" s="66">
+        <v>5.67</v>
+      </c>
+      <c r="G36" s="66">
+        <v>8.45</v>
+      </c>
+      <c r="H36" s="66">
+        <v>2.75</v>
+      </c>
+      <c r="I36" s="66">
+        <v>3.75</v>
+      </c>
+      <c r="J36" s="66">
+        <v>4.15</v>
+      </c>
+      <c r="K36" s="66">
+        <v>3.65</v>
+      </c>
+      <c r="L36" s="66">
+        <v>18.58</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B37">
+        <is>
+          <t xml:space="preserve">Jambi</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C37">
+        <is>
+          <t xml:space="preserve">Kab. Merangin</t>
+        </is>
+      </c>
+      <c r="D37" s="66">
+        <v>40.00</v>
+      </c>
+      <c r="E37" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="F37" s="66">
+        <v>11.00</v>
+      </c>
+      <c r="G37" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="H37" s="66">
+        <v>30.00</v>
+      </c>
+      <c r="I37" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="J37" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="K37" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="L37" s="66">
+        <v>2.00</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B38">
+        <is>
+          <t xml:space="preserve">Jambi</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C38">
+        <is>
+          <t xml:space="preserve">Kab. Bungo</t>
+        </is>
+      </c>
+      <c r="D38" s="66">
+        <v>60.50</v>
+      </c>
+      <c r="E38" s="66">
+        <v>4.10</v>
+      </c>
+      <c r="F38" s="66">
+        <v>14.10</v>
+      </c>
+      <c r="G38" s="66">
+        <v>5.90</v>
+      </c>
+      <c r="H38" s="66">
+        <v>1.80</v>
+      </c>
+      <c r="I38" s="66">
+        <v>1.50</v>
+      </c>
+      <c r="J38" s="66">
+        <v>5.15</v>
+      </c>
+      <c r="K38" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="L38" s="66">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B39">
+        <is>
+          <t xml:space="preserve">Jambi</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C39">
+        <is>
+          <t xml:space="preserve">Kota Jambi</t>
+        </is>
+      </c>
+      <c r="D39" s="66">
+        <v>16.11</v>
+      </c>
+      <c r="E39" s="66">
+        <v>23.84</v>
+      </c>
+      <c r="F39" s="66">
+        <v>7.38</v>
+      </c>
+      <c r="G39" s="66">
+        <v>44.07</v>
+      </c>
+      <c r="H39" s="66">
+        <v>0.89</v>
+      </c>
+      <c r="I39" s="66">
+        <v>0.57</v>
+      </c>
+      <c r="J39" s="66">
+        <v>1.23</v>
+      </c>
+      <c r="K39" s="66">
+        <v>0.30</v>
+      </c>
+      <c r="L39" s="66">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B40">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C40">
+        <is>
+          <t xml:space="preserve">Kab. Muara Enim</t>
+        </is>
+      </c>
+      <c r="D40" s="66">
+        <v>61.02</v>
+      </c>
+      <c r="E40" s="66">
+        <v>8.07</v>
+      </c>
+      <c r="F40" s="66">
+        <v>7.38</v>
+      </c>
+      <c r="G40" s="66">
+        <v>17.18</v>
+      </c>
+      <c r="H40" s="66">
+        <v>1.14</v>
+      </c>
+      <c r="I40" s="66">
+        <v>1.33</v>
+      </c>
+      <c r="J40" s="66">
+        <v>0.36</v>
+      </c>
+      <c r="K40" s="66">
+        <v>0.31</v>
+      </c>
+      <c r="L40" s="66">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B41">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C41">
+        <is>
+          <t xml:space="preserve">Kab. Lahat</t>
+        </is>
+      </c>
+      <c r="D41" s="66">
+        <v>50.00</v>
+      </c>
+      <c r="E41" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="F41" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="G41" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="H41" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="K41" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="L41" s="66">
+        <v>5.00</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B42">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C42">
+        <is>
+          <t xml:space="preserve">Kab. Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="D42" s="66">
+        <v>50.00</v>
+      </c>
+      <c r="E42" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="F42" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="G42" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="H42" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="I42" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="J42" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="K42" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="L42" s="66">
+        <v>1.00</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B43">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C43">
+        <is>
+          <t xml:space="preserve">Kab. Ogan Komering Ulu Timur</t>
+        </is>
+      </c>
+      <c r="D43" s="66">
+        <v>12.00</v>
+      </c>
+      <c r="E43" s="66">
+        <v>9.00</v>
+      </c>
+      <c r="F43" s="66">
+        <v>22.00</v>
+      </c>
+      <c r="G43" s="66">
+        <v>27.00</v>
+      </c>
+      <c r="H43" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="I43" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="J43" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="K43" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L43" s="66">
+        <v>17.00</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B44">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C44">
+        <is>
+          <t xml:space="preserve">Kota Palembang</t>
+        </is>
+      </c>
+      <c r="D44" s="66">
+        <v>56.90</v>
+      </c>
+      <c r="E44" s="66">
+        <v>5.40</v>
+      </c>
+      <c r="F44" s="66">
+        <v>15.10</v>
+      </c>
+      <c r="G44" s="66">
+        <v>17.50</v>
+      </c>
+      <c r="H44" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="I44" s="66">
+        <v>2.70</v>
+      </c>
+      <c r="J44" s="66">
+        <v>0.30</v>
+      </c>
+      <c r="K44" s="66">
+        <v>0.80</v>
+      </c>
+      <c r="L44" s="66">
+        <v>0.80</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B45">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C45">
+        <is>
+          <t xml:space="preserve">Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="D45" s="66">
+        <v>52.50</v>
+      </c>
+      <c r="E45" s="66">
+        <v>9.80</v>
+      </c>
+      <c r="F45" s="66">
+        <v>5.60</v>
+      </c>
+      <c r="G45" s="66">
+        <v>24.60</v>
+      </c>
+      <c r="H45" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="I45" s="66">
+        <v>1.80</v>
+      </c>
+      <c r="J45" s="66">
+        <v>0.80</v>
+      </c>
+      <c r="K45" s="66">
+        <v>1.70</v>
+      </c>
+      <c r="L45" s="66">
+        <v>1.20</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B46">
+        <is>
+          <t xml:space="preserve">Bengkulu</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C46">
+        <is>
+          <t xml:space="preserve">Kab. Seluma</t>
+        </is>
+      </c>
+      <c r="D46" s="66">
+        <v>45.00</v>
+      </c>
+      <c r="E46" s="66">
+        <v>35.00</v>
+      </c>
+      <c r="F46" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="G46" s="66">
+        <v>8.00</v>
+      </c>
+      <c r="H46" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="I46" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="K46" s="66">
+        <v>0.50</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B47">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C47">
+        <is>
+          <t xml:space="preserve">Kab. Tanggamus</t>
+        </is>
+      </c>
+      <c r="D47" s="66">
+        <v>36.32</v>
+      </c>
+      <c r="E47" s="66">
+        <v>22.03</v>
+      </c>
+      <c r="F47" s="66">
+        <v>8.92</v>
+      </c>
+      <c r="G47" s="66">
+        <v>16.80</v>
+      </c>
+      <c r="H47" s="66">
+        <v>4.07</v>
+      </c>
+      <c r="I47" s="66">
+        <v>3.08</v>
+      </c>
+      <c r="J47" s="66">
+        <v>2.58</v>
+      </c>
+      <c r="K47" s="66">
+        <v>4.86</v>
+      </c>
+      <c r="L47" s="66">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B48">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C48">
+        <is>
+          <t xml:space="preserve">Kab. Way Kanan</t>
+        </is>
+      </c>
+      <c r="D48" s="66">
+        <v>0.60</v>
+      </c>
+      <c r="E48" s="66">
+        <v>0.19</v>
+      </c>
+      <c r="F48" s="66">
+        <v>0.04</v>
+      </c>
+      <c r="G48" s="66">
+        <v>0.08</v>
+      </c>
+      <c r="H48" s="66">
+        <v>0.04</v>
+      </c>
+      <c r="I48" s="66">
+        <v>0.02</v>
+      </c>
+      <c r="J48" s="66">
+        <v>0.02</v>
+      </c>
+      <c r="K48" s="66">
+        <v>0.01</v>
+      </c>
+      <c r="L48" s="66">
+        <v>0.00</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B49">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C49">
+        <is>
+          <t xml:space="preserve">Kab. Pringsewu</t>
+        </is>
+      </c>
+      <c r="D49" s="66">
+        <v>33.00</v>
+      </c>
+      <c r="E49" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="F49" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="G49" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="H49" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="K49" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="L49" s="66">
+        <v>23.00</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B50">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C50">
+        <is>
+          <t xml:space="preserve">Kota Bandar Lampung</t>
+        </is>
+      </c>
+      <c r="D50" s="66">
+        <v>40.40</v>
+      </c>
+      <c r="E50" s="66">
+        <v>12.90</v>
+      </c>
+      <c r="F50" s="66">
+        <v>11.70</v>
+      </c>
+      <c r="G50" s="66">
+        <v>17.40</v>
+      </c>
+      <c r="H50" s="66">
+        <v>3.10</v>
+      </c>
+      <c r="I50" s="66">
+        <v>2.50</v>
+      </c>
+      <c r="J50" s="66">
+        <v>1.80</v>
+      </c>
+      <c r="K50" s="66">
+        <v>2.30</v>
+      </c>
+      <c r="L50" s="66">
+        <v>7.90</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B51">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C51">
+        <is>
+          <t xml:space="preserve">Kab. Bangka</t>
+        </is>
+      </c>
+      <c r="D51" s="66">
+        <v>39.85</v>
+      </c>
+      <c r="E51" s="66">
+        <v>13.96</v>
+      </c>
+      <c r="F51" s="66">
+        <v>12.07</v>
+      </c>
+      <c r="G51" s="66">
+        <v>16.97</v>
+      </c>
+      <c r="H51" s="66">
+        <v>3.37</v>
+      </c>
+      <c r="I51" s="66">
+        <v>2.69</v>
+      </c>
+      <c r="J51" s="66">
+        <v>1.98</v>
+      </c>
+      <c r="K51" s="66">
+        <v>2.31</v>
+      </c>
+      <c r="L51" s="66">
+        <v>6.80</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B52">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C52">
+        <is>
+          <t xml:space="preserve">Kab. Belitung</t>
+        </is>
+      </c>
+      <c r="D52" s="66">
+        <v>0.75</v>
+      </c>
+      <c r="E52" s="66">
+        <v>40.00</v>
+      </c>
+      <c r="F52" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="G52" s="66">
+        <v>30.00</v>
+      </c>
+      <c r="H52" s="66">
+        <v>2.50</v>
+      </c>
+      <c r="I52" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="J52" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="K52" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="L52" s="66">
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B53">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C53">
+        <is>
+          <t xml:space="preserve">Kab. Bangka Selatan</t>
+        </is>
+      </c>
+      <c r="D53" s="66">
+        <v>17.77</v>
+      </c>
+      <c r="E53" s="66">
+        <v>29.46</v>
+      </c>
+      <c r="F53" s="66">
+        <v>10.04</v>
+      </c>
+      <c r="G53" s="66">
+        <v>12.01</v>
+      </c>
+      <c r="H53" s="66">
+        <v>14.97</v>
+      </c>
+      <c r="I53" s="66">
+        <v>3.84</v>
+      </c>
+      <c r="J53" s="66">
+        <v>3.98</v>
+      </c>
+      <c r="K53" s="66">
+        <v>4.99</v>
+      </c>
+      <c r="L53" s="66">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B54">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C54">
+        <is>
+          <t xml:space="preserve">Kab. Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="D54" s="66">
+        <v>41.90</v>
+      </c>
+      <c r="E54" s="66">
+        <v>8.50</v>
+      </c>
+      <c r="F54" s="66">
+        <v>3.80</v>
+      </c>
+      <c r="G54" s="66">
+        <v>14.40</v>
+      </c>
+      <c r="H54" s="66">
+        <v>3.80</v>
+      </c>
+      <c r="I54" s="66">
+        <v>4.90</v>
+      </c>
+      <c r="J54" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K54" s="66">
+        <v>5.60</v>
+      </c>
+      <c r="L54" s="66">
+        <v>17.10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B55">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C55">
+        <is>
+          <t xml:space="preserve">Kota Pangkal Pinang</t>
+        </is>
+      </c>
+      <c r="D55" s="66">
+        <v>51.90</v>
+      </c>
+      <c r="E55" s="66">
+        <v>13.60</v>
+      </c>
+      <c r="F55" s="66">
+        <v>7.20</v>
+      </c>
+      <c r="G55" s="66">
+        <v>13.50</v>
+      </c>
+      <c r="H55" s="66">
+        <v>2.20</v>
+      </c>
+      <c r="I55" s="66">
+        <v>3.10</v>
+      </c>
+      <c r="J55" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K55" s="66">
+        <v>1.60</v>
+      </c>
+      <c r="L55" s="66">
+        <v>4.90</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B56">
+        <is>
+          <t xml:space="preserve">Kepulauan Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C56">
+        <is>
+          <t xml:space="preserve">Kab. Bintan</t>
+        </is>
+      </c>
+      <c r="D56" s="66">
+        <v>37.66</v>
+      </c>
+      <c r="E56" s="66">
+        <v>5.40</v>
+      </c>
+      <c r="F56" s="66">
+        <v>23.89</v>
+      </c>
+      <c r="G56" s="66">
+        <v>14.00</v>
+      </c>
+      <c r="H56" s="66">
+        <v>0.70</v>
+      </c>
+      <c r="I56" s="66">
+        <v>5.25</v>
+      </c>
+      <c r="J56" s="66">
+        <v>4.60</v>
+      </c>
+      <c r="K56" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="L56" s="66">
+        <v>5.50</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B57">
+        <is>
+          <t xml:space="preserve">Kepulauan Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C57">
+        <is>
+          <t xml:space="preserve">Kab. Karimun</t>
+        </is>
+      </c>
+      <c r="D57" s="66">
+        <v>23.00</v>
+      </c>
+      <c r="E57" s="66">
+        <v>19.00</v>
+      </c>
+      <c r="F57" s="66">
+        <v>24.00</v>
+      </c>
+      <c r="G57" s="66">
+        <v>24.50</v>
+      </c>
+      <c r="H57" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="I57" s="66">
+        <v>2.50</v>
+      </c>
+      <c r="J57" s="66">
+        <v>1.50</v>
+      </c>
+      <c r="K57" s="66">
+        <v>1.20</v>
+      </c>
+      <c r="L57" s="66">
+        <v>0.30</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B58">
+        <is>
+          <t xml:space="preserve">Kepulauan Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C58">
+        <is>
+          <t xml:space="preserve">Kota Tanjung Pinang</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B59">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C59">
+        <is>
+          <t xml:space="preserve">Kab. Adm. Kep. Seribu</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B60">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C60">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Pusat</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B61">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C61">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Utara</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B62">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C62">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Selatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B63">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C63">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Timur</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B64">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C64">
+        <is>
+          <t xml:space="preserve">Kab. Bandung</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B65">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C65">
+        <is>
+          <t xml:space="preserve">Kab. Garut</t>
+        </is>
+      </c>
+      <c r="D65" s="66">
+        <v>59.30</v>
+      </c>
+      <c r="F65" s="66">
+        <v>6.30</v>
+      </c>
+      <c r="G65" s="66">
+        <v>20.50</v>
+      </c>
+      <c r="H65" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="I65" s="66">
+        <v>2.60</v>
+      </c>
+      <c r="K65" s="66">
+        <v>3.40</v>
+      </c>
+      <c r="L65" s="66">
+        <v>6.90</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B66">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C66">
+        <is>
+          <t xml:space="preserve">Kab. Ciamis</t>
+        </is>
+      </c>
+      <c r="D66" s="66">
+        <v>34.40</v>
+      </c>
+      <c r="E66" s="66">
+        <v>0.40</v>
+      </c>
+      <c r="F66" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="G66" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="H66" s="66">
+        <v>10.70</v>
+      </c>
+      <c r="I66" s="66">
+        <v>6.40</v>
+      </c>
+      <c r="J66" s="66">
+        <v>1.70</v>
+      </c>
+      <c r="K66" s="66">
+        <v>16.10</v>
+      </c>
+      <c r="L66" s="66">
+        <v>0.30</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B67">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C67">
+        <is>
+          <t xml:space="preserve">Kab. Cirebon</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B68">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C68">
+        <is>
+          <t xml:space="preserve">Kab. Sumedang</t>
+        </is>
+      </c>
+      <c r="D68" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="E68" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="F68" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="G68" s="66">
+        <v>40.00</v>
+      </c>
+      <c r="H68" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="I68" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="J68" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K68" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L68" s="66">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B69">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C69">
+        <is>
+          <t xml:space="preserve">Kab. Indramayu</t>
+        </is>
+      </c>
+      <c r="D69" s="66">
+        <v>27.00</v>
+      </c>
+      <c r="E69" s="66">
+        <v>6.40</v>
+      </c>
+      <c r="F69" s="66">
+        <v>25.00</v>
+      </c>
+      <c r="G69" s="66">
+        <v>35.80</v>
+      </c>
+      <c r="H69" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="I69" s="66">
+        <v>1.80</v>
+      </c>
+      <c r="J69" s="66">
+        <v>0.80</v>
+      </c>
+      <c r="K69" s="66">
+        <v>0.70</v>
+      </c>
+      <c r="L69" s="66">
+        <v>1.50</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B70">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C70">
+        <is>
+          <t xml:space="preserve">Kota Bogor</t>
+        </is>
+      </c>
+      <c r="D70" s="66">
+        <v>40.00</v>
+      </c>
+      <c r="E70" s="66">
+        <v>14.00</v>
+      </c>
+      <c r="F70" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="G70" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="H70" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="I70" s="66">
+        <v>2.50</v>
+      </c>
+      <c r="J70" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="K70" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="L70" s="66">
+        <v>6.00</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B71">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C71">
+        <is>
+          <t xml:space="preserve">Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="D71" s="66">
+        <v>59.35</v>
+      </c>
+      <c r="F71" s="66">
+        <v>9.08</v>
+      </c>
+      <c r="G71" s="66">
+        <v>12.61</v>
+      </c>
+      <c r="H71" s="66">
+        <v>0.42</v>
+      </c>
+      <c r="I71" s="66">
+        <v>0.90</v>
+      </c>
+      <c r="K71" s="66">
+        <v>0.60</v>
+      </c>
+      <c r="L71" s="66">
+        <v>17.04</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B72">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C72">
+        <is>
+          <t xml:space="preserve">Kota Bandung</t>
+        </is>
+      </c>
+      <c r="D72" s="66">
+        <v>44.52</v>
+      </c>
+      <c r="E72" s="66">
+        <v>3.98</v>
+      </c>
+      <c r="F72" s="66">
+        <v>13.12</v>
+      </c>
+      <c r="G72" s="66">
+        <v>16.70</v>
+      </c>
+      <c r="H72" s="66">
+        <v>0.90</v>
+      </c>
+      <c r="I72" s="66">
+        <v>4.75</v>
+      </c>
+      <c r="J72" s="66">
+        <v>2.38</v>
+      </c>
+      <c r="K72" s="66">
+        <v>1.97</v>
+      </c>
+      <c r="L72" s="66">
+        <v>11.68</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B73">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C73">
+        <is>
+          <t xml:space="preserve">Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="D73" s="66">
+        <v>49.22</v>
+      </c>
+      <c r="E73" s="66">
+        <v>11.76</v>
+      </c>
+      <c r="F73" s="66">
+        <v>5.56</v>
+      </c>
+      <c r="G73" s="66">
+        <v>19.01</v>
+      </c>
+      <c r="H73" s="66">
+        <v>0.71</v>
+      </c>
+      <c r="I73" s="66">
+        <v>1.76</v>
+      </c>
+      <c r="J73" s="66">
+        <v>0.58</v>
+      </c>
+      <c r="K73" s="66">
+        <v>1.43</v>
+      </c>
+      <c r="L73" s="66">
+        <v>9.97</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B74">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C74">
+        <is>
+          <t xml:space="preserve">Kota Bekasi</t>
+        </is>
+      </c>
+      <c r="D74" s="66">
+        <v>65.20</v>
+      </c>
+      <c r="E74" s="66">
+        <v>7.20</v>
+      </c>
+      <c r="F74" s="66">
+        <v>4.20</v>
+      </c>
+      <c r="G74" s="66">
+        <v>15.60</v>
+      </c>
+      <c r="H74" s="66">
+        <v>0.20</v>
+      </c>
+      <c r="I74" s="66">
+        <v>6.30</v>
+      </c>
+      <c r="J74" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="K74" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="L74" s="66">
+        <v>0.30</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B75">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C75">
+        <is>
+          <t xml:space="preserve">Kota Depok</t>
+        </is>
+      </c>
+      <c r="D75" s="66">
+        <v>62.95</v>
+      </c>
+      <c r="E75" s="66">
+        <v>0.57</v>
+      </c>
+      <c r="F75" s="66">
+        <v>6.10</v>
+      </c>
+      <c r="G75" s="66">
+        <v>21.36</v>
+      </c>
+      <c r="H75" s="66">
+        <v>0.14</v>
+      </c>
+      <c r="I75" s="66">
+        <v>0.57</v>
+      </c>
+      <c r="J75" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="K75" s="66">
+        <v>0.57</v>
+      </c>
+      <c r="L75" s="66">
+        <v>7.24</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B76">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C76">
+        <is>
+          <t xml:space="preserve">Kota Cimahi</t>
+        </is>
+      </c>
+      <c r="E76" s="66">
+        <v>50.60</v>
+      </c>
+      <c r="F76" s="66">
+        <v>8.60</v>
+      </c>
+      <c r="G76" s="66">
+        <v>15.60</v>
+      </c>
+      <c r="H76" s="66">
+        <v>3.10</v>
+      </c>
+      <c r="I76" s="66">
+        <v>5.30</v>
+      </c>
+      <c r="K76" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="L76" s="66">
+        <v>13.80</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B77">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C77">
+        <is>
+          <t xml:space="preserve">Kab. Cilacap</t>
+        </is>
+      </c>
+      <c r="D77" s="66">
+        <v>57.67</v>
+      </c>
+      <c r="E77" s="66">
+        <v>10.63</v>
+      </c>
+      <c r="F77" s="66">
+        <v>9.71</v>
+      </c>
+      <c r="G77" s="66">
+        <v>16.42</v>
+      </c>
+      <c r="H77" s="66">
+        <v>1.33</v>
+      </c>
+      <c r="I77" s="66">
+        <v>1.25</v>
+      </c>
+      <c r="J77" s="66">
+        <v>0.51</v>
+      </c>
+      <c r="K77" s="66">
+        <v>0.65</v>
+      </c>
+      <c r="L77" s="66">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B78">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C78">
+        <is>
+          <t xml:space="preserve">Kab. Banyumas</t>
+        </is>
+      </c>
+      <c r="D78" s="66">
+        <v>36.00</v>
+      </c>
+      <c r="E78" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="F78" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="G78" s="66">
+        <v>30.00</v>
+      </c>
+      <c r="H78" s="66">
+        <v>9.00</v>
+      </c>
+      <c r="I78" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="J78" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="K78" s="66">
+        <v>5.00</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B79">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C79">
+        <is>
+          <t xml:space="preserve">Kab. Purbalingga</t>
+        </is>
+      </c>
+      <c r="D79" s="66">
+        <v>60.51</v>
+      </c>
+      <c r="E79" s="66">
+        <v>2.20</v>
+      </c>
+      <c r="F79" s="66">
+        <v>8.91</v>
+      </c>
+      <c r="G79" s="66">
+        <v>18.35</v>
+      </c>
+      <c r="H79" s="66">
+        <v>0.71</v>
+      </c>
+      <c r="I79" s="66">
+        <v>2.34</v>
+      </c>
+      <c r="J79" s="66">
+        <v>5.18</v>
+      </c>
+      <c r="K79" s="66">
+        <v>0.88</v>
+      </c>
+      <c r="L79" s="66">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B80">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C80">
+        <is>
+          <t xml:space="preserve">Kab. Purworejo</t>
+        </is>
+      </c>
+      <c r="D80" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="E80" s="66">
+        <v>67.00</v>
+      </c>
+      <c r="F80" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="G80" s="66">
+        <v>9.00</v>
+      </c>
+      <c r="H80" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="I80" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="J80" s="66">
+        <v>0.30</v>
+      </c>
+      <c r="K80" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="L80" s="66">
+        <v>8.20</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B81">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C81">
+        <is>
+          <t xml:space="preserve">Kab. Wonosobo</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B82">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C82">
+        <is>
+          <t xml:space="preserve">Kab. Magelang</t>
+        </is>
+      </c>
+      <c r="D82" s="66">
+        <v>37.80</v>
+      </c>
+      <c r="E82" s="66">
+        <v>3.90</v>
+      </c>
+      <c r="F82" s="66">
+        <v>26.20</v>
+      </c>
+      <c r="G82" s="66">
+        <v>17.90</v>
+      </c>
+      <c r="H82" s="66">
+        <v>1.30</v>
+      </c>
+      <c r="I82" s="66">
+        <v>1.10</v>
+      </c>
+      <c r="J82" s="66">
+        <v>0.80</v>
+      </c>
+      <c r="K82" s="66">
+        <v>2.40</v>
+      </c>
+      <c r="L82" s="66">
+        <v>8.60</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B83">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C83">
+        <is>
+          <t xml:space="preserve">Kab. Boyolali</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B84">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C84">
+        <is>
+          <t xml:space="preserve">Kab. Klaten</t>
+        </is>
+      </c>
+      <c r="D84" s="66">
+        <v>67.42</v>
+      </c>
+      <c r="E84" s="66">
+        <v>3.82</v>
+      </c>
+      <c r="F84" s="66">
+        <v>10.46</v>
+      </c>
+      <c r="G84" s="66">
+        <v>15.05</v>
+      </c>
+      <c r="H84" s="66">
+        <v>0.10</v>
+      </c>
+      <c r="I84" s="66">
+        <v>0.42</v>
+      </c>
+      <c r="J84" s="66">
+        <v>0.08</v>
+      </c>
+      <c r="K84" s="66">
+        <v>0.65</v>
+      </c>
+      <c r="L84" s="66">
+        <v>2.00</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B85">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C85">
+        <is>
+          <t xml:space="preserve">Kab. Sukoharjo</t>
+        </is>
+      </c>
+      <c r="D85" s="66">
+        <v>62.40</v>
+      </c>
+      <c r="E85" s="66">
+        <v>1.88</v>
+      </c>
+      <c r="F85" s="66">
+        <v>8.01</v>
+      </c>
+      <c r="G85" s="66">
+        <v>15.93</v>
+      </c>
+      <c r="H85" s="66">
+        <v>1.68</v>
+      </c>
+      <c r="I85" s="66">
+        <v>1.98</v>
+      </c>
+      <c r="J85" s="66">
+        <v>1.82</v>
+      </c>
+      <c r="K85" s="66">
+        <v>1.27</v>
+      </c>
+      <c r="L85" s="66">
+        <v>5.03</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B86">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C86">
+        <is>
+          <t xml:space="preserve">Kab. Wonogiri</t>
+        </is>
+      </c>
+      <c r="D86" s="66">
+        <v>25.00</v>
+      </c>
+      <c r="E86" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="F86" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="G86" s="66">
+        <v>25.00</v>
+      </c>
+      <c r="H86" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="I86" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="J86" s="66">
+        <v>2.50</v>
+      </c>
+      <c r="K86" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="L86" s="66">
+        <v>2.50</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B87">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C87">
+        <is>
+          <t xml:space="preserve">Kab. Karanganyar</t>
+        </is>
+      </c>
+      <c r="D87" s="66">
+        <v>63.00</v>
+      </c>
+      <c r="E87" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="F87" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="G87" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="H87" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="I87" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="J87" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K87" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="L87" s="66">
+        <v>2.00</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B88">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C88">
+        <is>
+          <t xml:space="preserve">Kab. Sragen</t>
+        </is>
+      </c>
+      <c r="D88" s="66">
+        <v>74.70</v>
+      </c>
+      <c r="E88" s="66">
+        <v>0.80</v>
+      </c>
+      <c r="F88" s="66">
+        <v>8.40</v>
+      </c>
+      <c r="G88" s="66">
+        <v>11.30</v>
+      </c>
+      <c r="H88" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="I88" s="66">
+        <v>1.90</v>
+      </c>
+      <c r="J88" s="66">
+        <v>0.30</v>
+      </c>
+      <c r="K88" s="66">
+        <v>1.80</v>
+      </c>
+      <c r="L88" s="66">
+        <v>0.30</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B89">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C89">
+        <is>
+          <t xml:space="preserve">Kab. Blora</t>
+        </is>
+      </c>
+      <c r="D89" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="E89" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="F89" s="66">
+        <v>18.00</v>
+      </c>
+      <c r="G89" s="66">
+        <v>40.00</v>
+      </c>
+      <c r="H89" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="I89" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="J89" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K89" s="66">
+        <v>2.50</v>
+      </c>
+      <c r="L89" s="66">
+        <v>0.50</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B90">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C90">
+        <is>
+          <t xml:space="preserve">Kab. Rembang</t>
+        </is>
+      </c>
+      <c r="D90" s="66">
+        <v>38.12</v>
+      </c>
+      <c r="E90" s="66">
+        <v>1.59</v>
+      </c>
+      <c r="F90" s="66">
+        <v>13.38</v>
+      </c>
+      <c r="G90" s="66">
+        <v>34.45</v>
+      </c>
+      <c r="H90" s="66">
+        <v>0.93</v>
+      </c>
+      <c r="I90" s="66">
+        <v>1.88</v>
+      </c>
+      <c r="J90" s="66">
+        <v>0.77</v>
+      </c>
+      <c r="K90" s="66">
+        <v>1.33</v>
+      </c>
+      <c r="L90" s="66">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B91">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C91">
+        <is>
+          <t xml:space="preserve">Kab. Pati</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B92">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C92">
+        <is>
+          <t xml:space="preserve">Kab. Jepara</t>
+        </is>
+      </c>
+      <c r="D92" s="66">
+        <v>32.24</v>
+      </c>
+      <c r="E92" s="66">
+        <v>22.75</v>
+      </c>
+      <c r="F92" s="66">
+        <v>10.86</v>
+      </c>
+      <c r="G92" s="66">
+        <v>21.70</v>
+      </c>
+      <c r="H92" s="66">
+        <v>0.78</v>
+      </c>
+      <c r="I92" s="66">
+        <v>2.12</v>
+      </c>
+      <c r="J92" s="66">
+        <v>0.53</v>
+      </c>
+      <c r="K92" s="66">
+        <v>1.68</v>
+      </c>
+      <c r="L92" s="66">
+        <v>7.34</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B93">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C93">
+        <is>
+          <t xml:space="preserve">Kab. Demak</t>
+        </is>
+      </c>
+      <c r="D93" s="66">
+        <v>32.30</v>
+      </c>
+      <c r="E93" s="66">
+        <v>20.76</v>
+      </c>
+      <c r="F93" s="66">
+        <v>9.06</v>
+      </c>
+      <c r="G93" s="66">
+        <v>23.07</v>
+      </c>
+      <c r="H93" s="66">
+        <v>0.60</v>
+      </c>
+      <c r="I93" s="66">
+        <v>1.77</v>
+      </c>
+      <c r="J93" s="66">
+        <v>0.44</v>
+      </c>
+      <c r="K93" s="66">
+        <v>1.23</v>
+      </c>
+      <c r="L93" s="66">
+        <v>10.77</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B94">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C94">
+        <is>
+          <t xml:space="preserve">Kab. Semarang</t>
+        </is>
+      </c>
+      <c r="D94" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="E94" s="66">
+        <v>9.00</v>
+      </c>
+      <c r="F94" s="66">
+        <v>23.00</v>
+      </c>
+      <c r="G94" s="66">
+        <v>30.00</v>
+      </c>
+      <c r="H94" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="I94" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="J94" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K94" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="L94" s="66">
+        <v>20.00</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B95">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C95">
+        <is>
+          <t xml:space="preserve">Kab. Temanggung</t>
+        </is>
+      </c>
+      <c r="D95" s="66">
+        <v>37.97</v>
+      </c>
+      <c r="E95" s="66">
+        <v>22.81</v>
+      </c>
+      <c r="F95" s="66">
+        <v>11.09</v>
+      </c>
+      <c r="G95" s="66">
+        <v>14.91</v>
+      </c>
+      <c r="H95" s="66">
+        <v>2.31</v>
+      </c>
+      <c r="I95" s="66">
+        <v>2.39</v>
+      </c>
+      <c r="J95" s="66">
+        <v>1.18</v>
+      </c>
+      <c r="K95" s="66">
+        <v>2.46</v>
+      </c>
+      <c r="L95" s="66">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B96">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C96">
+        <is>
+          <t xml:space="preserve">Kab. Batang</t>
+        </is>
+      </c>
+      <c r="D96" s="66">
+        <v>28.00</v>
+      </c>
+      <c r="E96" s="66">
+        <v>13.00</v>
+      </c>
+      <c r="F96" s="66">
+        <v>13.00</v>
+      </c>
+      <c r="G96" s="66">
+        <v>16.00</v>
+      </c>
+      <c r="H96" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="I96" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="J96" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="K96" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="L96" s="66">
+        <v>8.00</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B97">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C97">
+        <is>
+          <t xml:space="preserve">Kab. Pekalongan</t>
+        </is>
+      </c>
+      <c r="D97" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="E97" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="F97" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="G97" s="66">
+        <v>9.00</v>
+      </c>
+      <c r="H97" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="I97" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="J97" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="L97" s="66">
+        <v>71.00</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B98">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C98">
+        <is>
+          <t xml:space="preserve">Kab. Pemalang</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B99">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C99">
+        <is>
+          <t xml:space="preserve">Kab. Tegal</t>
+        </is>
+      </c>
+      <c r="D99" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="E99" s="66">
+        <v>16.00</v>
+      </c>
+      <c r="F99" s="66">
+        <v>18.00</v>
+      </c>
+      <c r="G99" s="66">
+        <v>33.00</v>
+      </c>
+      <c r="H99" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="I99" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="J99" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K99" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="L99" s="66">
+        <v>5.00</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B100">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C100">
+        <is>
+          <t xml:space="preserve">Kab. Brebes</t>
+        </is>
+      </c>
+      <c r="D100" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="E100" s="66">
+        <v>80.00</v>
+      </c>
+      <c r="F100" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="G100" s="66">
+        <v>11.00</v>
+      </c>
+      <c r="H100" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="I100" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="J100" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="K100" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="L100" s="66">
+        <v>1.00</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B101">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C101">
+        <is>
+          <t xml:space="preserve">Kota Magelang</t>
+        </is>
+      </c>
+      <c r="D101" s="66">
+        <v>33.70</v>
+      </c>
+      <c r="E101" s="66">
+        <v>13.30</v>
+      </c>
+      <c r="F101" s="66">
+        <v>18.80</v>
+      </c>
+      <c r="G101" s="66">
+        <v>21.50</v>
+      </c>
+      <c r="H101" s="66">
+        <v>0.80</v>
+      </c>
+      <c r="I101" s="66">
+        <v>1.80</v>
+      </c>
+      <c r="J101" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="K101" s="66">
+        <v>3.70</v>
+      </c>
+      <c r="L101" s="66">
+        <v>5.90</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B102">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C102">
+        <is>
+          <t xml:space="preserve">Kota Salatiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B103">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C103">
+        <is>
+          <t xml:space="preserve">Kota Semarang</t>
+        </is>
+      </c>
+      <c r="D103" s="66">
+        <v>60.79</v>
+      </c>
+      <c r="F103" s="66">
+        <v>10.18</v>
+      </c>
+      <c r="G103" s="66">
+        <v>17.20</v>
+      </c>
+      <c r="H103" s="66">
+        <v>1.22</v>
+      </c>
+      <c r="I103" s="66">
+        <v>4.94</v>
+      </c>
+      <c r="J103" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="K103" s="66">
+        <v>1.79</v>
+      </c>
+      <c r="L103" s="66">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B104">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C104">
+        <is>
+          <t xml:space="preserve">Kota Tegal</t>
+        </is>
+      </c>
+      <c r="D104" s="66">
+        <v>54.00</v>
+      </c>
+      <c r="E104" s="66">
+        <v>11.00</v>
+      </c>
+      <c r="F104" s="66">
+        <v>8.50</v>
+      </c>
+      <c r="G104" s="66">
+        <v>14.00</v>
+      </c>
+      <c r="H104" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="I104" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="J104" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K104" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L104" s="66">
+        <v>0.50</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B105">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C105">
+        <is>
+          <t xml:space="preserve">Kab. Kulon Progo</t>
+        </is>
+      </c>
+      <c r="D105" s="66">
+        <v>67.18</v>
+      </c>
+      <c r="F105" s="66">
+        <v>12.60</v>
+      </c>
+      <c r="G105" s="66">
+        <v>17.22</v>
+      </c>
+      <c r="H105" s="66">
+        <v>1.68</v>
+      </c>
+      <c r="I105" s="66">
+        <v>0.21</v>
+      </c>
+      <c r="K105" s="66">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B106">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C106">
+        <is>
+          <t xml:space="preserve">Kab. Sleman</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B107">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C107">
+        <is>
+          <t xml:space="preserve">Kota Yogyakarta</t>
+        </is>
+      </c>
+      <c r="D107" s="66">
+        <v>50.21</v>
+      </c>
+      <c r="E107" s="66">
+        <v>10.91</v>
+      </c>
+      <c r="F107" s="66">
+        <v>6.18</v>
+      </c>
+      <c r="G107" s="66">
+        <v>10.79</v>
+      </c>
+      <c r="H107" s="66">
+        <v>2.12</v>
+      </c>
+      <c r="I107" s="66">
+        <v>0.68</v>
+      </c>
+      <c r="J107" s="66">
+        <v>0.13</v>
+      </c>
+      <c r="K107" s="66">
+        <v>10.66</v>
+      </c>
+      <c r="L107" s="66">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B108">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C108">
+        <is>
+          <t xml:space="preserve">Kab. Pacitan</t>
+        </is>
+      </c>
+      <c r="D108" s="66">
+        <v>68.40</v>
+      </c>
+      <c r="E108" s="66">
+        <v>2.90</v>
+      </c>
+      <c r="F108" s="66">
+        <v>8.30</v>
+      </c>
+      <c r="G108" s="66">
+        <v>17.00</v>
+      </c>
+      <c r="H108" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="I108" s="66">
+        <v>0.20</v>
+      </c>
+      <c r="J108" s="66">
+        <v>0.20</v>
+      </c>
+      <c r="K108" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="L108" s="66">
+        <v>2.00</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B109">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C109">
+        <is>
+          <t xml:space="preserve">Kab. Ponorogo</t>
+        </is>
+      </c>
+      <c r="D109" s="66">
+        <v>44.76</v>
+      </c>
+      <c r="E109" s="66">
+        <v>0.36</v>
+      </c>
+      <c r="F109" s="66">
+        <v>16.53</v>
+      </c>
+      <c r="G109" s="66">
+        <v>21.89</v>
+      </c>
+      <c r="H109" s="66">
+        <v>0.48</v>
+      </c>
+      <c r="I109" s="66">
+        <v>6.61</v>
+      </c>
+      <c r="J109" s="66">
+        <v>1.43</v>
+      </c>
+      <c r="K109" s="66">
+        <v>0.60</v>
+      </c>
+      <c r="L109" s="66">
+        <v>7.34</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B110">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C110">
+        <is>
+          <t xml:space="preserve">Kab. Trenggalek</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B111">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C111">
+        <is>
+          <t xml:space="preserve">Kab. Tulungagung</t>
+        </is>
+      </c>
+      <c r="D111" s="66">
+        <v>48.00</v>
+      </c>
+      <c r="E111" s="66">
+        <v>16.00</v>
+      </c>
+      <c r="F111" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="G111" s="66">
+        <v>6.50</v>
+      </c>
+      <c r="H111" s="66">
+        <v>9.00</v>
+      </c>
+      <c r="I111" s="66">
+        <v>6.70</v>
+      </c>
+      <c r="J111" s="66">
+        <v>2.50</v>
+      </c>
+      <c r="K111" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L111" s="66">
+        <v>2.30</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B112">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C112">
+        <is>
+          <t xml:space="preserve">Kab. Blitar</t>
+        </is>
+      </c>
+      <c r="D112" s="66">
+        <v>70.85</v>
+      </c>
+      <c r="E112" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="F112" s="66">
+        <v>12.45</v>
+      </c>
+      <c r="G112" s="66">
+        <v>7.50</v>
+      </c>
+      <c r="H112" s="66">
+        <v>0.90</v>
+      </c>
+      <c r="I112" s="66">
+        <v>1.94</v>
+      </c>
+      <c r="J112" s="66">
+        <v>0.52</v>
+      </c>
+      <c r="K112" s="66">
+        <v>0.92</v>
+      </c>
+      <c r="L112" s="66">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B113">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C113">
+        <is>
+          <t xml:space="preserve">Kab. Kediri</t>
+        </is>
+      </c>
+      <c r="D113" s="66">
+        <v>46.40</v>
+      </c>
+      <c r="E113" s="66">
+        <v>22.47</v>
+      </c>
+      <c r="F113" s="66">
+        <v>4.28</v>
+      </c>
+      <c r="G113" s="66">
+        <v>11.31</v>
+      </c>
+      <c r="H113" s="66">
+        <v>0.20</v>
+      </c>
+      <c r="I113" s="66">
+        <v>2.02</v>
+      </c>
+      <c r="J113" s="66">
+        <v>0.63</v>
+      </c>
+      <c r="K113" s="66">
+        <v>4.75</v>
+      </c>
+      <c r="L113" s="66">
+        <v>7.94</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B114">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C114">
+        <is>
+          <t xml:space="preserve">Kab. Lumajang</t>
+        </is>
+      </c>
+      <c r="D114" s="66">
+        <v>40.25</v>
+      </c>
+      <c r="E114" s="66">
+        <v>17.35</v>
+      </c>
+      <c r="F114" s="66">
+        <v>10.65</v>
+      </c>
+      <c r="G114" s="66">
+        <v>17.80</v>
+      </c>
+      <c r="H114" s="66">
+        <v>1.15</v>
+      </c>
+      <c r="I114" s="66">
+        <v>3.25</v>
+      </c>
+      <c r="J114" s="66">
+        <v>1.45</v>
+      </c>
+      <c r="K114" s="66">
+        <v>1.50</v>
+      </c>
+      <c r="L114" s="66">
+        <v>6.60</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B115">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C115">
+        <is>
+          <t xml:space="preserve">Kab. Banyuwangi</t>
+        </is>
+      </c>
+      <c r="D115" s="66">
+        <v>3.12</v>
+      </c>
+      <c r="E115" s="66">
+        <v>0.84</v>
+      </c>
+      <c r="F115" s="66">
+        <v>18.98</v>
+      </c>
+      <c r="G115" s="66">
+        <v>21.78</v>
+      </c>
+      <c r="H115" s="66">
+        <v>0.94</v>
+      </c>
+      <c r="I115" s="66">
+        <v>1.52</v>
+      </c>
+      <c r="J115" s="66">
+        <v>0.57</v>
+      </c>
+      <c r="K115" s="66">
+        <v>2.55</v>
+      </c>
+      <c r="L115" s="66">
+        <v>49.70</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B116">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C116">
+        <is>
+          <t xml:space="preserve">Kab. Situbondo</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B117">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C117">
+        <is>
+          <t xml:space="preserve">Kab. Jombang</t>
+        </is>
+      </c>
+      <c r="D117" s="66">
+        <v>48.85</v>
+      </c>
+      <c r="E117" s="66">
+        <v>7.27</v>
+      </c>
+      <c r="F117" s="66">
+        <v>7.93</v>
+      </c>
+      <c r="G117" s="66">
+        <v>12.50</v>
+      </c>
+      <c r="H117" s="66">
+        <v>1.24</v>
+      </c>
+      <c r="I117" s="66">
+        <v>2.71</v>
+      </c>
+      <c r="J117" s="66">
+        <v>1.33</v>
+      </c>
+      <c r="K117" s="66">
+        <v>1.24</v>
+      </c>
+      <c r="L117" s="66">
+        <v>16.93</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B118">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C118">
+        <is>
+          <t xml:space="preserve">Kab. Nganjuk</t>
+        </is>
+      </c>
+      <c r="D118" s="66">
+        <v>61.50</v>
+      </c>
+      <c r="E118" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="F118" s="66">
+        <v>13.10</v>
+      </c>
+      <c r="G118" s="66">
+        <v>12.30</v>
+      </c>
+      <c r="H118" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="I118" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="J118" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="K118" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="L118" s="66">
+        <v>2.10</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B119">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C119">
+        <is>
+          <t xml:space="preserve">Kab. Magetan</t>
+        </is>
+      </c>
+      <c r="D119" s="66">
+        <v>25.00</v>
+      </c>
+      <c r="E119" s="66">
+        <v>25.00</v>
+      </c>
+      <c r="F119" s="66">
+        <v>8.00</v>
+      </c>
+      <c r="G119" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="H119" s="66">
+        <v>1.50</v>
+      </c>
+      <c r="I119" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="J119" s="66">
+        <v>1.80</v>
+      </c>
+      <c r="K119" s="66">
+        <v>1.30</v>
+      </c>
+      <c r="L119" s="66">
+        <v>15.40</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B120">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C120">
+        <is>
+          <t xml:space="preserve">Kab. Ngawi</t>
+        </is>
+      </c>
+      <c r="D120" s="66">
+        <v>38.30</v>
+      </c>
+      <c r="E120" s="66">
+        <v>3.80</v>
+      </c>
+      <c r="F120" s="66">
+        <v>10.40</v>
+      </c>
+      <c r="G120" s="66">
+        <v>30.60</v>
+      </c>
+      <c r="H120" s="66">
+        <v>2.40</v>
+      </c>
+      <c r="I120" s="66">
+        <v>2.30</v>
+      </c>
+      <c r="J120" s="66">
+        <v>3.70</v>
+      </c>
+      <c r="K120" s="66">
+        <v>3.50</v>
+      </c>
+      <c r="L120" s="66">
+        <v>5.00</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B121">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C121">
+        <is>
+          <t xml:space="preserve">Kab. Bojonegoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B122">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C122">
+        <is>
+          <t xml:space="preserve">Kab. Tuban</t>
+        </is>
+      </c>
+      <c r="D122" s="66">
+        <v>58.52</v>
+      </c>
+      <c r="E122" s="66">
+        <v>15.32</v>
+      </c>
+      <c r="F122" s="66">
+        <v>5.78</v>
+      </c>
+      <c r="G122" s="66">
+        <v>11.02</v>
+      </c>
+      <c r="H122" s="66">
+        <v>0.17</v>
+      </c>
+      <c r="I122" s="66">
+        <v>1.62</v>
+      </c>
+      <c r="J122" s="66">
+        <v>0.10</v>
+      </c>
+      <c r="K122" s="66">
+        <v>1.33</v>
+      </c>
+      <c r="L122" s="66">
+        <v>6.14</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B123">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C123">
+        <is>
+          <t xml:space="preserve">Kab. Lamongan</t>
+        </is>
+      </c>
+      <c r="D123" s="66">
+        <v>30.00</v>
+      </c>
+      <c r="E123" s="66">
+        <v>12.00</v>
+      </c>
+      <c r="F123" s="66">
+        <v>9.00</v>
+      </c>
+      <c r="G123" s="66">
+        <v>18.00</v>
+      </c>
+      <c r="H123" s="66">
+        <v>8.00</v>
+      </c>
+      <c r="I123" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="J123" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K123" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="L123" s="66">
+        <v>18.00</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B124">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C124">
+        <is>
+          <t xml:space="preserve">Kab. Pamekasan</t>
+        </is>
+      </c>
+      <c r="D124" s="66">
+        <v>55.00</v>
+      </c>
+      <c r="E124" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="F124" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="G124" s="66">
+        <v>13.00</v>
+      </c>
+      <c r="H124" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="I124" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="J124" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K124" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L124" s="66">
+        <v>9.00</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B125">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C125">
+        <is>
+          <t xml:space="preserve">Kab. Sumenep</t>
+        </is>
+      </c>
+      <c r="D125" s="66">
+        <v>58.62</v>
+      </c>
+      <c r="E125" s="66">
+        <v>1.08</v>
+      </c>
+      <c r="F125" s="66">
+        <v>20.83</v>
+      </c>
+      <c r="G125" s="66">
+        <v>17.33</v>
+      </c>
+      <c r="I125" s="66">
+        <v>0.91</v>
+      </c>
+      <c r="J125" s="66">
+        <v>0.26</v>
+      </c>
+      <c r="K125" s="66">
+        <v>0.57</v>
+      </c>
+      <c r="L125" s="66">
+        <v>0.40</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B126">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C126">
+        <is>
+          <t xml:space="preserve">Kota Kediri</t>
+        </is>
+      </c>
+      <c r="D126" s="66">
+        <v>54.20</v>
+      </c>
+      <c r="E126" s="66">
+        <v>7.70</v>
+      </c>
+      <c r="F126" s="66">
+        <v>12.40</v>
+      </c>
+      <c r="G126" s="66">
+        <v>14.50</v>
+      </c>
+      <c r="H126" s="66">
+        <v>4.70</v>
+      </c>
+      <c r="I126" s="66">
+        <v>2.20</v>
+      </c>
+      <c r="J126" s="66">
+        <v>1.40</v>
+      </c>
+      <c r="K126" s="66">
+        <v>0.80</v>
+      </c>
+      <c r="L126" s="66">
+        <v>2.10</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B127">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C127">
+        <is>
+          <t xml:space="preserve">Kota Blitar</t>
+        </is>
+      </c>
+      <c r="D127" s="66">
+        <v>53.00</v>
+      </c>
+      <c r="E127" s="66">
+        <v>13.60</v>
+      </c>
+      <c r="F127" s="66">
+        <v>5.20</v>
+      </c>
+      <c r="G127" s="66">
+        <v>9.10</v>
+      </c>
+      <c r="H127" s="66">
+        <v>0.80</v>
+      </c>
+      <c r="I127" s="66">
+        <v>2.90</v>
+      </c>
+      <c r="J127" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="K127" s="66">
+        <v>3.40</v>
+      </c>
+      <c r="L127" s="66">
+        <v>9.00</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B128">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C128">
+        <is>
+          <t xml:space="preserve">Kota Malang</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B129">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C129">
+        <is>
+          <t xml:space="preserve">Kota Probolinggo</t>
+        </is>
+      </c>
+      <c r="D129" s="66">
+        <v>60.98</v>
+      </c>
+      <c r="E129" s="66">
+        <v>3.68</v>
+      </c>
+      <c r="F129" s="66">
+        <v>10.56</v>
+      </c>
+      <c r="G129" s="66">
+        <v>19.87</v>
+      </c>
+      <c r="H129" s="66">
+        <v>0.82</v>
+      </c>
+      <c r="I129" s="66">
+        <v>0.78</v>
+      </c>
+      <c r="J129" s="66">
+        <v>0.93</v>
+      </c>
+      <c r="K129" s="66">
+        <v>0.96</v>
+      </c>
+      <c r="L129" s="66">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B130">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C130">
+        <is>
+          <t xml:space="preserve">Kota Pasuruan</t>
+        </is>
+      </c>
+      <c r="D130" s="66">
+        <v>10.11</v>
+      </c>
+      <c r="E130" s="66">
+        <v>6.40</v>
+      </c>
+      <c r="F130" s="66">
+        <v>1.35</v>
+      </c>
+      <c r="G130" s="66">
+        <v>6.06</v>
+      </c>
+      <c r="H130" s="66">
+        <v>0.07</v>
+      </c>
+      <c r="I130" s="66">
+        <v>0.67</v>
+      </c>
+      <c r="J130" s="66">
+        <v>0.07</v>
+      </c>
+      <c r="K130" s="66">
+        <v>0.13</v>
+      </c>
+      <c r="L130" s="66">
+        <v>75.14</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B131">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C131">
+        <is>
+          <t xml:space="preserve">Kota Madiun</t>
+        </is>
+      </c>
+      <c r="D131" s="66">
+        <v>81.00</v>
+      </c>
+      <c r="E131" s="66">
+        <v>1.50</v>
+      </c>
+      <c r="F131" s="66">
+        <v>7.90</v>
+      </c>
+      <c r="G131" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="H131" s="66">
+        <v>2.50</v>
+      </c>
+      <c r="I131" s="66">
+        <v>0.90</v>
+      </c>
+      <c r="J131" s="66">
+        <v>0.90</v>
+      </c>
+      <c r="K131" s="66">
+        <v>0.80</v>
+      </c>
+      <c r="L131" s="66">
+        <v>0.50</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B132">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C132">
+        <is>
+          <t xml:space="preserve">Kota Surabaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B133">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C133">
+        <is>
+          <t xml:space="preserve">Kota Batu</t>
+        </is>
+      </c>
+      <c r="D133" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="E133" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="F133" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="G133" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="H133" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="K133" s="66">
+        <v>1.00</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B134">
+        <is>
+          <t xml:space="preserve">Banten</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C134">
+        <is>
+          <t xml:space="preserve">Kab. Serang</t>
+        </is>
+      </c>
+      <c r="D134" s="66">
+        <v>63.01</v>
+      </c>
+      <c r="F134" s="66">
+        <v>9.13</v>
+      </c>
+      <c r="G134" s="66">
+        <v>20.02</v>
+      </c>
+      <c r="H134" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="I134" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K134" s="66">
+        <v>0.28</v>
+      </c>
+      <c r="L134" s="66">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B135">
+        <is>
+          <t xml:space="preserve">Banten</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C135">
+        <is>
+          <t xml:space="preserve">Kota Cilegon</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B136">
+        <is>
+          <t xml:space="preserve">Banten</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C136">
+        <is>
+          <t xml:space="preserve">Kota Tangerang Selatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B137">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C137">
+        <is>
+          <t xml:space="preserve">Kab. Jembrana</t>
+        </is>
+      </c>
+      <c r="D137" s="66">
+        <v>11.22</v>
+      </c>
+      <c r="E137" s="66">
+        <v>30.88</v>
+      </c>
+      <c r="F137" s="66">
+        <v>11.10</v>
+      </c>
+      <c r="G137" s="66">
+        <v>22.10</v>
+      </c>
+      <c r="H137" s="66">
+        <v>2.10</v>
+      </c>
+      <c r="I137" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="J137" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="K137" s="66">
+        <v>2.70</v>
+      </c>
+      <c r="L137" s="66">
+        <v>5.90</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B138">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C138">
+        <is>
+          <t xml:space="preserve">Kab. Tabanan</t>
+        </is>
+      </c>
+      <c r="D138" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="E138" s="66">
+        <v>39.00</v>
+      </c>
+      <c r="F138" s="66">
+        <v>37.00</v>
+      </c>
+      <c r="G138" s="66">
+        <v>42.00</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B139">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C139">
+        <is>
+          <t xml:space="preserve">Kab. Badung</t>
+        </is>
+      </c>
+      <c r="D139" s="66">
+        <v>16.00</v>
+      </c>
+      <c r="E139" s="66">
+        <v>33.90</v>
+      </c>
+      <c r="F139" s="66">
+        <v>11.10</v>
+      </c>
+      <c r="G139" s="66">
+        <v>28.40</v>
+      </c>
+      <c r="H139" s="66">
+        <v>2.60</v>
+      </c>
+      <c r="I139" s="66">
+        <v>2.10</v>
+      </c>
+      <c r="J139" s="66">
+        <v>0.67</v>
+      </c>
+      <c r="K139" s="66">
+        <v>0.90</v>
+      </c>
+      <c r="L139" s="66">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B140">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C140">
+        <is>
+          <t xml:space="preserve">Kab. Gianyar</t>
+        </is>
+      </c>
+      <c r="E140" s="66">
+        <v>58.73</v>
+      </c>
+      <c r="F140" s="66">
+        <v>10.89</v>
+      </c>
+      <c r="G140" s="66">
+        <v>17.08</v>
+      </c>
+      <c r="H140" s="66">
+        <v>3.15</v>
+      </c>
+      <c r="I140" s="66">
+        <v>0.76</v>
+      </c>
+      <c r="J140" s="66">
+        <v>0.74</v>
+      </c>
+      <c r="L140" s="66">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B141">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C141">
+        <is>
+          <t xml:space="preserve">Kab. Bangli</t>
+        </is>
+      </c>
+      <c r="D141" s="66">
+        <v>12.00</v>
+      </c>
+      <c r="E141" s="66">
+        <v>70.00</v>
+      </c>
+      <c r="F141" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="G141" s="66">
+        <v>3.80</v>
+      </c>
+      <c r="H141" s="66">
+        <v>1.50</v>
+      </c>
+      <c r="I141" s="66">
+        <v>0.40</v>
+      </c>
+      <c r="J141" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="K141" s="66">
+        <v>0.80</v>
+      </c>
+      <c r="L141" s="66">
+        <v>9.00</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B142">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C142">
+        <is>
+          <t xml:space="preserve">Kab. Buleleng</t>
+        </is>
+      </c>
+      <c r="D142" s="66">
+        <v>2.99</v>
+      </c>
+      <c r="E142" s="66">
+        <v>62.57</v>
+      </c>
+      <c r="F142" s="66">
+        <v>5.63</v>
+      </c>
+      <c r="G142" s="66">
+        <v>10.18</v>
+      </c>
+      <c r="H142" s="66">
+        <v>2.82</v>
+      </c>
+      <c r="I142" s="66">
+        <v>5.33</v>
+      </c>
+      <c r="J142" s="66">
+        <v>4.55</v>
+      </c>
+      <c r="K142" s="66">
+        <v>3.33</v>
+      </c>
+      <c r="L142" s="66">
+        <v>2.60</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B143">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C143">
+        <is>
+          <t xml:space="preserve">Kota Denpasar</t>
+        </is>
+      </c>
+      <c r="D143" s="66">
+        <v>29.30</v>
+      </c>
+      <c r="E143" s="66">
+        <v>33.90</v>
+      </c>
+      <c r="F143" s="66">
+        <v>6.90</v>
+      </c>
+      <c r="G143" s="66">
+        <v>13.70</v>
+      </c>
+      <c r="H143" s="66">
+        <v>0.80</v>
+      </c>
+      <c r="I143" s="66">
+        <v>0.70</v>
+      </c>
+      <c r="J143" s="66">
+        <v>0.30</v>
+      </c>
+      <c r="K143" s="66">
+        <v>2.10</v>
+      </c>
+      <c r="L143" s="66">
+        <v>12.30</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B144">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C144">
+        <is>
+          <t xml:space="preserve">Kab. Lombok Timur</t>
+        </is>
+      </c>
+      <c r="D144" s="66">
+        <v>36.00</v>
+      </c>
+      <c r="E144" s="66">
+        <v>23.00</v>
+      </c>
+      <c r="F144" s="66">
+        <v>3.50</v>
+      </c>
+      <c r="G144" s="66">
+        <v>19.00</v>
+      </c>
+      <c r="H144" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="I144" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="J144" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="K144" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="L144" s="66">
+        <v>0.50</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B145">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C145">
+        <is>
+          <t xml:space="preserve">Kab. Sumbawa</t>
+        </is>
+      </c>
+      <c r="D145" s="66">
+        <v>38.21</v>
+      </c>
+      <c r="E145" s="66">
+        <v>8.18</v>
+      </c>
+      <c r="F145" s="66">
+        <v>12.19</v>
+      </c>
+      <c r="G145" s="66">
+        <v>20.34</v>
+      </c>
+      <c r="H145" s="66">
+        <v>2.36</v>
+      </c>
+      <c r="I145" s="66">
+        <v>0.51</v>
+      </c>
+      <c r="J145" s="66">
+        <v>0.68</v>
+      </c>
+      <c r="K145" s="66">
+        <v>4.28</v>
+      </c>
+      <c r="L145" s="66">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B146">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C146">
+        <is>
+          <t xml:space="preserve">Kota Mataram</t>
+        </is>
+      </c>
+      <c r="D146" s="66">
+        <v>64.00</v>
+      </c>
+      <c r="E146" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="F146" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="G146" s="66">
+        <v>9.00</v>
+      </c>
+      <c r="H146" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="I146" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="J146" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K146" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L146" s="66">
+        <v>2.00</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B147">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C147">
+        <is>
+          <t xml:space="preserve">Kab. Alor</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B148">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C148">
+        <is>
+          <t xml:space="preserve">Kab. Manggarai Barat</t>
+        </is>
+      </c>
+      <c r="D148" s="66">
+        <v>34.79</v>
+      </c>
+      <c r="E148" s="66">
+        <v>17.00</v>
+      </c>
+      <c r="F148" s="66">
+        <v>23.31</v>
+      </c>
+      <c r="G148" s="66">
+        <v>11.10</v>
+      </c>
+      <c r="H148" s="66">
+        <v>2.65</v>
+      </c>
+      <c r="I148" s="66">
+        <v>3.27</v>
+      </c>
+      <c r="J148" s="66">
+        <v>1.35</v>
+      </c>
+      <c r="K148" s="66">
+        <v>2.97</v>
+      </c>
+      <c r="L148" s="66">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B149">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C149">
+        <is>
+          <t xml:space="preserve">Kota Kupang</t>
+        </is>
+      </c>
+      <c r="D149" s="66">
+        <v>28.50</v>
+      </c>
+      <c r="E149" s="66">
+        <v>16.50</v>
+      </c>
+      <c r="F149" s="66">
+        <v>14.00</v>
+      </c>
+      <c r="G149" s="66">
+        <v>20.50</v>
+      </c>
+      <c r="H149" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="I149" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="J149" s="66">
+        <v>1.50</v>
+      </c>
+      <c r="K149" s="66">
+        <v>2.50</v>
+      </c>
+      <c r="L149" s="66">
+        <v>8.50</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B150">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C150">
+        <is>
+          <t xml:space="preserve">Kab. Sambas</t>
+        </is>
+      </c>
+      <c r="D150" s="66">
+        <v>40.00</v>
+      </c>
+      <c r="E150" s="66">
+        <v>5.60</v>
+      </c>
+      <c r="F150" s="66">
+        <v>14.20</v>
+      </c>
+      <c r="G150" s="66">
+        <v>25.00</v>
+      </c>
+      <c r="H150" s="66">
+        <v>0.30</v>
+      </c>
+      <c r="I150" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="J150" s="66">
+        <v>0.90</v>
+      </c>
+      <c r="K150" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L150" s="66">
+        <v>11.00</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B151">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C151">
+        <is>
+          <t xml:space="preserve">Kab. Mempawah</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B152">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C152">
+        <is>
+          <t xml:space="preserve">Kab. Sanggau</t>
+        </is>
+      </c>
+      <c r="D152" s="66">
+        <v>56.21</v>
+      </c>
+      <c r="E152" s="66">
+        <v>13.61</v>
+      </c>
+      <c r="F152" s="66">
+        <v>4.73</v>
+      </c>
+      <c r="G152" s="66">
+        <v>7.10</v>
+      </c>
+      <c r="K152" s="66">
+        <v>2.96</v>
+      </c>
+      <c r="L152" s="66">
+        <v>15.39</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B153">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C153">
+        <is>
+          <t xml:space="preserve">Kab. Melawi</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B154">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C154">
+        <is>
+          <t xml:space="preserve">Kota Pontianak</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B155">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C155">
+        <is>
+          <t xml:space="preserve">Kota Singkawang</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B156">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C156">
+        <is>
+          <t xml:space="preserve">Kab. Kapuas</t>
+        </is>
+      </c>
+      <c r="D156" s="66">
+        <v>30.00</v>
+      </c>
+      <c r="E156" s="66">
+        <v>22.00</v>
+      </c>
+      <c r="F156" s="66">
+        <v>18.00</v>
+      </c>
+      <c r="G156" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="H156" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="L156" s="66">
+        <v>4.00</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B157">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C157">
+        <is>
+          <t xml:space="preserve">Kab. Barito Utara</t>
+        </is>
+      </c>
+      <c r="D157" s="66">
+        <v>30.00</v>
+      </c>
+      <c r="E157" s="66">
+        <v>12.00</v>
+      </c>
+      <c r="F157" s="66">
+        <v>14.00</v>
+      </c>
+      <c r="G157" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="H157" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="I157" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="J157" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K157" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L157" s="66">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B158">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C158">
+        <is>
+          <t xml:space="preserve">Kab. Seruyan</t>
+        </is>
+      </c>
+      <c r="D158" s="66">
+        <v>30.00</v>
+      </c>
+      <c r="E158" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="F158" s="66">
+        <v>10.50</v>
+      </c>
+      <c r="G158" s="66">
+        <v>25.00</v>
+      </c>
+      <c r="H158" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="I158" s="66">
+        <v>1.50</v>
+      </c>
+      <c r="J158" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="K158" s="66">
+        <v>2.50</v>
+      </c>
+      <c r="L158" s="66">
+        <v>8.50</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B159">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C159">
+        <is>
+          <t xml:space="preserve">Kab. Gunung Mas</t>
+        </is>
+      </c>
+      <c r="D159" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="E159" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="F159" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="G159" s="66">
+        <v>50.00</v>
+      </c>
+      <c r="H159" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="I159" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="J159" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K159" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="L159" s="66">
+        <v>0.50</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B160">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C160">
+        <is>
+          <t xml:space="preserve">Kab. Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="D160" s="66">
+        <v>23.51</v>
+      </c>
+      <c r="E160" s="66">
+        <v>26.74</v>
+      </c>
+      <c r="F160" s="66">
+        <v>13.31</v>
+      </c>
+      <c r="G160" s="66">
+        <v>25.13</v>
+      </c>
+      <c r="H160" s="66">
+        <v>3.19</v>
+      </c>
+      <c r="I160" s="66">
+        <v>2.41</v>
+      </c>
+      <c r="J160" s="66">
+        <v>0.83</v>
+      </c>
+      <c r="K160" s="66">
+        <v>1.79</v>
+      </c>
+      <c r="L160" s="66">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B161">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C161">
+        <is>
+          <t xml:space="preserve">Kab. Barito Timur</t>
+        </is>
+      </c>
+      <c r="D161" s="66">
+        <v>32.00</v>
+      </c>
+      <c r="E161" s="66">
+        <v>9.00</v>
+      </c>
+      <c r="F161" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="G161" s="66">
+        <v>37.00</v>
+      </c>
+      <c r="H161" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="I161" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="J161" s="66">
+        <v>6.50</v>
+      </c>
+      <c r="K161" s="66">
+        <v>1.20</v>
+      </c>
+      <c r="L161" s="66">
+        <v>1.30</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B162">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C162">
+        <is>
+          <t xml:space="preserve">Kota Palangkaraya</t>
+        </is>
+      </c>
+      <c r="D162" s="66">
+        <v>42.04</v>
+      </c>
+      <c r="E162" s="66">
+        <v>4.33</v>
+      </c>
+      <c r="F162" s="66">
+        <v>8.54</v>
+      </c>
+      <c r="G162" s="66">
+        <v>19.49</v>
+      </c>
+      <c r="H162" s="66">
+        <v>1.28</v>
+      </c>
+      <c r="I162" s="66">
+        <v>2.36</v>
+      </c>
+      <c r="J162" s="66">
+        <v>2.18</v>
+      </c>
+      <c r="K162" s="66">
+        <v>2.04</v>
+      </c>
+      <c r="L162" s="66">
+        <v>17.73</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B163">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C163">
+        <is>
+          <t xml:space="preserve">Kab. Tanah Laut</t>
+        </is>
+      </c>
+      <c r="D163" s="66">
+        <v>40.00</v>
+      </c>
+      <c r="E163" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="F163" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="G163" s="66">
+        <v>14.00</v>
+      </c>
+      <c r="H163" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="I163" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="J163" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="K163" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L163" s="66">
+        <v>2.00</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B164">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C164">
+        <is>
+          <t xml:space="preserve">Kab. Kotabaru</t>
+        </is>
+      </c>
+      <c r="D164" s="66">
+        <v>34.00</v>
+      </c>
+      <c r="E164" s="66">
+        <v>13.00</v>
+      </c>
+      <c r="F164" s="66">
+        <v>27.00</v>
+      </c>
+      <c r="G164" s="66">
+        <v>11.00</v>
+      </c>
+      <c r="H164" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="I164" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="J164" s="66">
+        <v>0.20</v>
+      </c>
+      <c r="K164" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="L164" s="66">
+        <v>11.80</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B165">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C165">
+        <is>
+          <t xml:space="preserve">Kab. Banjar</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B166">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C166">
+        <is>
+          <t xml:space="preserve">Kab. Barito Kuala</t>
+        </is>
+      </c>
+      <c r="D166" s="66">
+        <v>59.50</v>
+      </c>
+      <c r="E166" s="66">
+        <v>9.50</v>
+      </c>
+      <c r="F166" s="66">
+        <v>10.50</v>
+      </c>
+      <c r="G166" s="66">
+        <v>12.00</v>
+      </c>
+      <c r="H166" s="66">
+        <v>3.10</v>
+      </c>
+      <c r="I166" s="66">
+        <v>1.90</v>
+      </c>
+      <c r="J166" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="K166" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L166" s="66">
+        <v>1.00</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B167">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C167">
+        <is>
+          <t xml:space="preserve">Kab. Tapin</t>
+        </is>
+      </c>
+      <c r="D167" s="66">
+        <v>50.24</v>
+      </c>
+      <c r="E167" s="66">
+        <v>3.58</v>
+      </c>
+      <c r="F167" s="66">
+        <v>10.50</v>
+      </c>
+      <c r="G167" s="66">
+        <v>33.40</v>
+      </c>
+      <c r="H167" s="66">
+        <v>0.48</v>
+      </c>
+      <c r="I167" s="66">
+        <v>0.88</v>
+      </c>
+      <c r="J167" s="66">
+        <v>0.15</v>
+      </c>
+      <c r="K167" s="66">
+        <v>0.12</v>
+      </c>
+      <c r="L167" s="66">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B168">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C168">
+        <is>
+          <t xml:space="preserve">Kab. Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="D168" s="66">
+        <v>55.18</v>
+      </c>
+      <c r="E168" s="66">
+        <v>1.48</v>
+      </c>
+      <c r="F168" s="66">
+        <v>13.13</v>
+      </c>
+      <c r="G168" s="66">
+        <v>25.35</v>
+      </c>
+      <c r="H168" s="66">
+        <v>2.90</v>
+      </c>
+      <c r="I168" s="66">
+        <v>0.46</v>
+      </c>
+      <c r="J168" s="66">
+        <v>0.90</v>
+      </c>
+      <c r="K168" s="66">
+        <v>0.40</v>
+      </c>
+      <c r="L168" s="66">
+        <v>0.20</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B169">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C169">
+        <is>
+          <t xml:space="preserve">Kab. Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="D169" s="66">
+        <v>40.04</v>
+      </c>
+      <c r="E169" s="66">
+        <v>1.40</v>
+      </c>
+      <c r="F169" s="66">
+        <v>4.05</v>
+      </c>
+      <c r="G169" s="66">
+        <v>24.91</v>
+      </c>
+      <c r="H169" s="66">
+        <v>3.63</v>
+      </c>
+      <c r="I169" s="66">
+        <v>1.05</v>
+      </c>
+      <c r="J169" s="66">
+        <v>1.24</v>
+      </c>
+      <c r="K169" s="66">
+        <v>1.47</v>
+      </c>
+      <c r="L169" s="66">
+        <v>22.21</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B170">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C170">
+        <is>
+          <t xml:space="preserve">Kab. Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="D170" s="66">
+        <v>50.63</v>
+      </c>
+      <c r="E170" s="66">
+        <v>9.21</v>
+      </c>
+      <c r="F170" s="66">
+        <v>9.83</v>
+      </c>
+      <c r="G170" s="66">
+        <v>13.78</v>
+      </c>
+      <c r="H170" s="66">
+        <v>0.85</v>
+      </c>
+      <c r="I170" s="66">
+        <v>0.65</v>
+      </c>
+      <c r="J170" s="66">
+        <v>1.09</v>
+      </c>
+      <c r="K170" s="66">
+        <v>7.80</v>
+      </c>
+      <c r="L170" s="66">
+        <v>6.16</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B171">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C171">
+        <is>
+          <t xml:space="preserve">Kab. Tabalong</t>
+        </is>
+      </c>
+      <c r="D171" s="66">
+        <v>36.00</v>
+      </c>
+      <c r="E171" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="F171" s="66">
+        <v>17.00</v>
+      </c>
+      <c r="G171" s="66">
+        <v>24.00</v>
+      </c>
+      <c r="H171" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="I171" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="K171" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="L171" s="66">
+        <v>14.00</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B172">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C172">
+        <is>
+          <t xml:space="preserve">Kab. Tanah Bumbu</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B173">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C173">
+        <is>
+          <t xml:space="preserve">Kab. Balangan</t>
+        </is>
+      </c>
+      <c r="D173" s="66">
+        <v>57.46</v>
+      </c>
+      <c r="E173" s="66">
+        <v>10.24</v>
+      </c>
+      <c r="F173" s="66">
+        <v>10.95</v>
+      </c>
+      <c r="G173" s="66">
+        <v>14.62</v>
+      </c>
+      <c r="H173" s="66">
+        <v>2.06</v>
+      </c>
+      <c r="I173" s="66">
+        <v>1.67</v>
+      </c>
+      <c r="J173" s="66">
+        <v>0.72</v>
+      </c>
+      <c r="K173" s="66">
+        <v>1.20</v>
+      </c>
+      <c r="L173" s="66">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B174">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C174">
+        <is>
+          <t xml:space="preserve">Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="D174" s="66">
+        <v>55.89</v>
+      </c>
+      <c r="E174" s="66">
+        <v>0.64</v>
+      </c>
+      <c r="F174" s="66">
+        <v>9.39</v>
+      </c>
+      <c r="G174" s="66">
+        <v>12.77</v>
+      </c>
+      <c r="H174" s="66">
+        <v>1.36</v>
+      </c>
+      <c r="I174" s="66">
+        <v>14.93</v>
+      </c>
+      <c r="J174" s="66">
+        <v>1.63</v>
+      </c>
+      <c r="K174" s="66">
+        <v>2.71</v>
+      </c>
+      <c r="L174" s="66">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B175">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C175">
+        <is>
+          <t xml:space="preserve">Kota Banjarbaru</t>
+        </is>
+      </c>
+      <c r="D175" s="66">
+        <v>48.30</v>
+      </c>
+      <c r="E175" s="66">
+        <v>4.20</v>
+      </c>
+      <c r="F175" s="66">
+        <v>16.00</v>
+      </c>
+      <c r="G175" s="66">
+        <v>23.70</v>
+      </c>
+      <c r="H175" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="I175" s="66">
+        <v>0.30</v>
+      </c>
+      <c r="J175" s="66">
+        <v>0.40</v>
+      </c>
+      <c r="K175" s="66">
+        <v>0.10</v>
+      </c>
+      <c r="L175" s="66">
+        <v>6.50</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B176">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C176">
+        <is>
+          <t xml:space="preserve">Kab. Paser</t>
+        </is>
+      </c>
+      <c r="D176" s="66">
+        <v>54.99</v>
+      </c>
+      <c r="E176" s="66">
+        <v>0.22</v>
+      </c>
+      <c r="F176" s="66">
+        <v>10.20</v>
+      </c>
+      <c r="G176" s="66">
+        <v>13.64</v>
+      </c>
+      <c r="H176" s="66">
+        <v>1.38</v>
+      </c>
+      <c r="I176" s="66">
+        <v>13.56</v>
+      </c>
+      <c r="J176" s="66">
+        <v>1.20</v>
+      </c>
+      <c r="K176" s="66">
+        <v>3.52</v>
+      </c>
+      <c r="L176" s="66">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B177">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C177">
+        <is>
+          <t xml:space="preserve">Kab. Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="D177" s="66">
+        <v>73.92</v>
+      </c>
+      <c r="E177" s="66">
+        <v>0.98</v>
+      </c>
+      <c r="F177" s="66">
+        <v>10.43</v>
+      </c>
+      <c r="G177" s="66">
+        <v>7.86</v>
+      </c>
+      <c r="H177" s="66">
+        <v>2.04</v>
+      </c>
+      <c r="I177" s="66">
+        <v>1.57</v>
+      </c>
+      <c r="J177" s="66">
+        <v>0.55</v>
+      </c>
+      <c r="K177" s="66">
+        <v>1.75</v>
+      </c>
+      <c r="L177" s="66">
+        <v>0.90</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B178">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C178">
+        <is>
+          <t xml:space="preserve">Kab. Kutai Timur</t>
+        </is>
+      </c>
+      <c r="D178" s="66">
+        <v>43.00</v>
+      </c>
+      <c r="E178" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="F178" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="G178" s="66">
+        <v>22.00</v>
+      </c>
+      <c r="H178" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="I178" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="J178" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K178" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L178" s="66">
+        <v>1.00</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B179">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C179">
+        <is>
+          <t xml:space="preserve">Kab. Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="D179" s="66">
+        <v>46.13</v>
+      </c>
+      <c r="E179" s="66">
+        <v>1.09</v>
+      </c>
+      <c r="F179" s="66">
+        <v>20.87</v>
+      </c>
+      <c r="G179" s="66">
+        <v>29.83</v>
+      </c>
+      <c r="H179" s="66">
+        <v>0.22</v>
+      </c>
+      <c r="I179" s="66">
+        <v>0.02</v>
+      </c>
+      <c r="J179" s="66">
+        <v>0.67</v>
+      </c>
+      <c r="K179" s="66">
+        <v>0.83</v>
+      </c>
+      <c r="L179" s="66">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B180">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C180">
+        <is>
+          <t xml:space="preserve">Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="D180" s="66">
+        <v>42.30</v>
+      </c>
+      <c r="E180" s="66">
+        <v>6.36</v>
+      </c>
+      <c r="F180" s="66">
+        <v>10.26</v>
+      </c>
+      <c r="G180" s="66">
+        <v>7.20</v>
+      </c>
+      <c r="H180" s="66">
+        <v>3.87</v>
+      </c>
+      <c r="I180" s="66">
+        <v>2.94</v>
+      </c>
+      <c r="J180" s="66">
+        <v>0.98</v>
+      </c>
+      <c r="K180" s="66">
+        <v>6.56</v>
+      </c>
+      <c r="L180" s="66">
+        <v>19.53</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B181">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C181">
+        <is>
+          <t xml:space="preserve">Kota Samarinda</t>
+        </is>
+      </c>
+      <c r="D181" s="66">
+        <v>53.39</v>
+      </c>
+      <c r="E181" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="F181" s="66">
+        <v>17.00</v>
+      </c>
+      <c r="G181" s="66">
+        <v>19.90</v>
+      </c>
+      <c r="H181" s="66">
+        <v>0.65</v>
+      </c>
+      <c r="I181" s="66">
+        <v>0.62</v>
+      </c>
+      <c r="J181" s="66">
+        <v>0.06</v>
+      </c>
+      <c r="K181" s="66">
+        <v>0.92</v>
+      </c>
+      <c r="L181" s="66">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B182">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C182">
+        <is>
+          <t xml:space="preserve">Kota Bontang</t>
+        </is>
+      </c>
+      <c r="D182" s="66">
+        <v>44.12</v>
+      </c>
+      <c r="E182" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="F182" s="66">
+        <v>27.50</v>
+      </c>
+      <c r="G182" s="66">
+        <v>18.00</v>
+      </c>
+      <c r="H182" s="66">
+        <v>2.10</v>
+      </c>
+      <c r="I182" s="66">
+        <v>0.03</v>
+      </c>
+      <c r="J182" s="66">
+        <v>0.25</v>
+      </c>
+      <c r="K182" s="66">
+        <v>1.05</v>
+      </c>
+      <c r="L182" s="66">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B183">
+        <is>
+          <t xml:space="preserve">Kalimantan Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C183">
+        <is>
+          <t xml:space="preserve">Kab. Nunukan</t>
+        </is>
+      </c>
+      <c r="D183" s="66">
+        <v>46.40</v>
+      </c>
+      <c r="E183" s="66">
+        <v>8.20</v>
+      </c>
+      <c r="F183" s="66">
+        <v>23.40</v>
+      </c>
+      <c r="G183" s="66">
+        <v>21.30</v>
+      </c>
+      <c r="H183" s="66">
+        <v>0.20</v>
+      </c>
+      <c r="I183" s="66">
+        <v>0.20</v>
+      </c>
+      <c r="J183" s="66">
+        <v>0.10</v>
+      </c>
+      <c r="K183" s="66">
+        <v>0.10</v>
+      </c>
+      <c r="L183" s="66">
+        <v>0.10</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B184">
+        <is>
+          <t xml:space="preserve">Kalimantan Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C184">
+        <is>
+          <t xml:space="preserve">Kab. Tana Tidung</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B185">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C185">
+        <is>
+          <t xml:space="preserve">Kab. Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="D185" s="66">
+        <v>51.10</v>
+      </c>
+      <c r="E185" s="66">
+        <v>4.89</v>
+      </c>
+      <c r="F185" s="66">
+        <v>5.20</v>
+      </c>
+      <c r="G185" s="66">
+        <v>26.00</v>
+      </c>
+      <c r="H185" s="66">
+        <v>0.40</v>
+      </c>
+      <c r="I185" s="66">
+        <v>3.30</v>
+      </c>
+      <c r="J185" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="K185" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L185" s="66">
+        <v>6.61</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B186">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C186">
+        <is>
+          <t xml:space="preserve">Kab. Minahasa Selatan</t>
+        </is>
+      </c>
+      <c r="D186" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="E186" s="66">
+        <v>12.00</v>
+      </c>
+      <c r="F186" s="66">
+        <v>12.00</v>
+      </c>
+      <c r="G186" s="66">
+        <v>36.00</v>
+      </c>
+      <c r="H186" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="I186" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="J186" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="K186" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L186" s="66">
+        <v>5.00</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B187">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C187">
+        <is>
+          <t xml:space="preserve">Kab. Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="D187" s="66">
+        <v>36.08</v>
+      </c>
+      <c r="E187" s="66">
+        <v>9.68</v>
+      </c>
+      <c r="F187" s="66">
+        <v>12.16</v>
+      </c>
+      <c r="G187" s="66">
+        <v>11.04</v>
+      </c>
+      <c r="H187" s="66">
+        <v>4.28</v>
+      </c>
+      <c r="I187" s="66">
+        <v>4.26</v>
+      </c>
+      <c r="J187" s="66">
+        <v>3.24</v>
+      </c>
+      <c r="K187" s="66">
+        <v>5.14</v>
+      </c>
+      <c r="L187" s="66">
+        <v>14.12</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B188">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C188">
+        <is>
+          <t xml:space="preserve">Kab. Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="D188" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="E188" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="F188" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="G188" s="66">
+        <v>8.00</v>
+      </c>
+      <c r="H188" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="I188" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="J188" s="66">
+        <v>0.30</v>
+      </c>
+      <c r="K188" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="L188" s="66">
+        <v>71.70</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B189">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C189">
+        <is>
+          <t xml:space="preserve">Kab. Bolaang Mongondow Selatan</t>
+        </is>
+      </c>
+      <c r="D189" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="E189" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="F189" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="G189" s="66">
+        <v>25.00</v>
+      </c>
+      <c r="H189" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="I189" s="66">
+        <v>12.00</v>
+      </c>
+      <c r="J189" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="K189" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="L189" s="66">
+        <v>3.00</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B190">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C190">
+        <is>
+          <t xml:space="preserve">Kota Manado</t>
+        </is>
+      </c>
+      <c r="D190" s="66">
+        <v>47.70</v>
+      </c>
+      <c r="E190" s="66">
+        <v>1.14</v>
+      </c>
+      <c r="F190" s="66">
+        <v>18.66</v>
+      </c>
+      <c r="G190" s="66">
+        <v>19.48</v>
+      </c>
+      <c r="H190" s="66">
+        <v>0.26</v>
+      </c>
+      <c r="I190" s="66">
+        <v>1.54</v>
+      </c>
+      <c r="J190" s="66">
+        <v>1.49</v>
+      </c>
+      <c r="K190" s="66">
+        <v>1.85</v>
+      </c>
+      <c r="L190" s="66">
+        <v>7.88</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B191">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C191">
+        <is>
+          <t xml:space="preserve">Kota Bitung</t>
+        </is>
+      </c>
+      <c r="D191" s="66">
+        <v>48.20</v>
+      </c>
+      <c r="E191" s="66">
+        <v>2.05</v>
+      </c>
+      <c r="F191" s="66">
+        <v>18.03</v>
+      </c>
+      <c r="G191" s="66">
+        <v>19.07</v>
+      </c>
+      <c r="H191" s="66">
+        <v>0.36</v>
+      </c>
+      <c r="I191" s="66">
+        <v>1.48</v>
+      </c>
+      <c r="J191" s="66">
+        <v>1.37</v>
+      </c>
+      <c r="K191" s="66">
+        <v>1.83</v>
+      </c>
+      <c r="L191" s="66">
+        <v>7.61</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B192">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C192">
+        <is>
+          <t xml:space="preserve">Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="D192" s="66">
+        <v>53.50</v>
+      </c>
+      <c r="E192" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="F192" s="66">
+        <v>11.80</v>
+      </c>
+      <c r="G192" s="66">
+        <v>8.50</v>
+      </c>
+      <c r="H192" s="66">
+        <v>5.70</v>
+      </c>
+      <c r="I192" s="66">
+        <v>3.60</v>
+      </c>
+      <c r="J192" s="66">
+        <v>2.60</v>
+      </c>
+      <c r="K192" s="66">
+        <v>2.80</v>
+      </c>
+      <c r="L192" s="66">
+        <v>6.50</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B193">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C193">
+        <is>
+          <t xml:space="preserve">Kab. Donggala</t>
+        </is>
+      </c>
+      <c r="D193" s="66">
+        <v>35.00</v>
+      </c>
+      <c r="E193" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="F193" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="G193" s="66">
+        <v>13.00</v>
+      </c>
+      <c r="H193" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="I193" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="J193" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="K193" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="L193" s="66">
+        <v>7.00</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B194">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C194">
+        <is>
+          <t xml:space="preserve">Kab. Parigi Moutong</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B195">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C195">
+        <is>
+          <t xml:space="preserve">Kab. Sigi</t>
+        </is>
+      </c>
+      <c r="L195" s="66">
+        <v>0.00</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B196">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C196">
+        <is>
+          <t xml:space="preserve">Kab. Banggai Laut</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B197">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C197">
+        <is>
+          <t xml:space="preserve">Kota Palu</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B198">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C198">
+        <is>
+          <t xml:space="preserve">Kab. Kepulauan Selayar</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B199">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C199">
+        <is>
+          <t xml:space="preserve">Kab. Bulukumba</t>
+        </is>
+      </c>
+      <c r="D199" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="E199" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="F199" s="66">
+        <v>25.00</v>
+      </c>
+      <c r="G199" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="H199" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="I199" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="J199" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="K199" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="L199" s="66">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B200">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C200">
+        <is>
+          <t xml:space="preserve">Kab. Bantaeng</t>
+        </is>
+      </c>
+      <c r="D200" s="66">
+        <v>30.13</v>
+      </c>
+      <c r="E200" s="66">
+        <v>27.50</v>
+      </c>
+      <c r="F200" s="66">
+        <v>11.00</v>
+      </c>
+      <c r="G200" s="66">
+        <v>14.00</v>
+      </c>
+      <c r="H200" s="66">
+        <v>1.24</v>
+      </c>
+      <c r="I200" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="J200" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K200" s="66">
+        <v>1.13</v>
+      </c>
+      <c r="L200" s="66">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B201">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C201">
+        <is>
+          <t xml:space="preserve">Kab. Jeneponto</t>
+        </is>
+      </c>
+      <c r="D201" s="66">
+        <v>27.00</v>
+      </c>
+      <c r="E201" s="66">
+        <v>18.00</v>
+      </c>
+      <c r="F201" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="G201" s="66">
+        <v>18.00</v>
+      </c>
+      <c r="H201" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="I201" s="66">
+        <v>1.50</v>
+      </c>
+      <c r="J201" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="K201" s="66">
+        <v>1.50</v>
+      </c>
+      <c r="L201" s="66">
+        <v>13.00</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B202">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C202">
+        <is>
+          <t xml:space="preserve">Kab. Sinjai</t>
+        </is>
+      </c>
+      <c r="D202" s="66">
+        <v>31.50</v>
+      </c>
+      <c r="E202" s="66">
+        <v>13.00</v>
+      </c>
+      <c r="F202" s="66">
+        <v>31.09</v>
+      </c>
+      <c r="G202" s="66">
+        <v>14.68</v>
+      </c>
+      <c r="H202" s="66">
+        <v>8.20</v>
+      </c>
+      <c r="I202" s="66">
+        <v>0.87</v>
+      </c>
+      <c r="J202" s="66">
+        <v>0.44</v>
+      </c>
+      <c r="K202" s="66">
+        <v>0.08</v>
+      </c>
+      <c r="L202" s="66">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B203">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C203">
+        <is>
+          <t xml:space="preserve">Kab. Bone</t>
+        </is>
+      </c>
+      <c r="D203" s="66">
+        <v>73.20</v>
+      </c>
+      <c r="E203" s="66">
+        <v>0.50</v>
+      </c>
+      <c r="F203" s="66">
+        <v>10.10</v>
+      </c>
+      <c r="G203" s="66">
+        <v>8.70</v>
+      </c>
+      <c r="H203" s="66">
+        <v>3.10</v>
+      </c>
+      <c r="I203" s="66">
+        <v>0.30</v>
+      </c>
+      <c r="J203" s="66">
+        <v>1.10</v>
+      </c>
+      <c r="K203" s="66">
+        <v>1.10</v>
+      </c>
+      <c r="L203" s="66">
+        <v>1.90</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B204">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C204">
+        <is>
+          <t xml:space="preserve">Kab. Maros</t>
+        </is>
+      </c>
+      <c r="D204" s="66">
+        <v>73.98</v>
+      </c>
+      <c r="E204" s="66">
+        <v>7.90</v>
+      </c>
+      <c r="F204" s="66">
+        <v>3.18</v>
+      </c>
+      <c r="G204" s="66">
+        <v>7.86</v>
+      </c>
+      <c r="H204" s="66">
+        <v>2.21</v>
+      </c>
+      <c r="I204" s="66">
+        <v>0.57</v>
+      </c>
+      <c r="J204" s="66">
+        <v>0.55</v>
+      </c>
+      <c r="K204" s="66">
+        <v>0.25</v>
+      </c>
+      <c r="L204" s="66">
+        <v>3.50</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B205">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C205">
+        <is>
+          <t xml:space="preserve">Kab. Pangkajene dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="D205" s="66">
+        <v>63.13</v>
+      </c>
+      <c r="E205" s="66">
+        <v>10.83</v>
+      </c>
+      <c r="F205" s="66">
+        <v>8.99</v>
+      </c>
+      <c r="G205" s="66">
+        <v>7.29</v>
+      </c>
+      <c r="H205" s="66">
+        <v>6.50</v>
+      </c>
+      <c r="I205" s="66">
+        <v>0.72</v>
+      </c>
+      <c r="J205" s="66">
+        <v>0.19</v>
+      </c>
+      <c r="K205" s="66">
+        <v>1.55</v>
+      </c>
+      <c r="L205" s="66">
+        <v>0.80</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B206">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C206">
+        <is>
+          <t xml:space="preserve">Kab. Barru</t>
+        </is>
+      </c>
+      <c r="D206" s="66">
+        <v>57.00</v>
+      </c>
+      <c r="E206" s="66">
+        <v>12.50</v>
+      </c>
+      <c r="F206" s="66">
+        <v>6.00</v>
+      </c>
+      <c r="G206" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="H206" s="66">
+        <v>2.50</v>
+      </c>
+      <c r="I206" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="J206" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="K206" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="L206" s="66">
+        <v>4.00</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B207">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C207">
+        <is>
+          <t xml:space="preserve">Kab. Soppeng</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B208">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C208">
+        <is>
+          <t xml:space="preserve">Kab. Wajo</t>
+        </is>
+      </c>
+      <c r="D208" s="66">
+        <v>41.03</v>
+      </c>
+      <c r="E208" s="66">
+        <v>17.34</v>
+      </c>
+      <c r="F208" s="66">
+        <v>7.20</v>
+      </c>
+      <c r="G208" s="66">
+        <v>17.02</v>
+      </c>
+      <c r="H208" s="66">
+        <v>2.10</v>
+      </c>
+      <c r="I208" s="66">
+        <v>3.90</v>
+      </c>
+      <c r="J208" s="66">
+        <v>6.40</v>
+      </c>
+      <c r="K208" s="66">
+        <v>2.90</v>
+      </c>
+      <c r="L208" s="66">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B209">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C209">
+        <is>
+          <t xml:space="preserve">Kab. Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="D209" s="66">
+        <v>56.00</v>
+      </c>
+      <c r="E209" s="66">
+        <v>9.60</v>
+      </c>
+      <c r="F209" s="66">
+        <v>6.20</v>
+      </c>
+      <c r="G209" s="66">
+        <v>6.60</v>
+      </c>
+      <c r="H209" s="66">
+        <v>4.50</v>
+      </c>
+      <c r="I209" s="66">
+        <v>3.60</v>
+      </c>
+      <c r="J209" s="66">
+        <v>4.20</v>
+      </c>
+      <c r="K209" s="66">
+        <v>4.40</v>
+      </c>
+      <c r="L209" s="66">
+        <v>4.90</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B210">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C210">
+        <is>
+          <t xml:space="preserve">Kab. Pinrang</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B211">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C211">
+        <is>
+          <t xml:space="preserve">Kab. Enrekang</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B212">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C212">
+        <is>
+          <t xml:space="preserve">Kab. Luwu Timur</t>
+        </is>
+      </c>
+      <c r="D212" s="66">
+        <v>40.00</v>
+      </c>
+      <c r="E212" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="F212" s="66">
+        <v>25.00</v>
+      </c>
+      <c r="G212" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="H212" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="I212" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="J212" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="K212" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L212" s="66">
+        <v>2.00</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B213">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C213">
+        <is>
+          <t xml:space="preserve">Kota Makassar</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B214">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C214">
+        <is>
+          <t xml:space="preserve">Kota Parepare</t>
+        </is>
+      </c>
+      <c r="D214" s="66">
+        <v>51.80</v>
+      </c>
+      <c r="E214" s="66">
+        <v>11.35</v>
+      </c>
+      <c r="F214" s="66">
+        <v>12.45</v>
+      </c>
+      <c r="G214" s="66">
+        <v>11.20</v>
+      </c>
+      <c r="H214" s="66">
+        <v>3.75</v>
+      </c>
+      <c r="I214" s="66">
+        <v>1.95</v>
+      </c>
+      <c r="J214" s="66">
+        <v>2.10</v>
+      </c>
+      <c r="K214" s="66">
+        <v>2.75</v>
+      </c>
+      <c r="L214" s="66">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B215">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C215">
+        <is>
+          <t xml:space="preserve">Kota Palopo</t>
+        </is>
+      </c>
+      <c r="D215" s="66">
+        <v>30.00</v>
+      </c>
+      <c r="E215" s="66">
+        <v>25.00</v>
+      </c>
+      <c r="F215" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="G215" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="H215" s="66">
+        <v>8.00</v>
+      </c>
+      <c r="L215" s="66">
+        <v>2.00</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B216">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C216">
+        <is>
+          <t xml:space="preserve">Kab. Wakatobi</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B217">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C217">
+        <is>
+          <t xml:space="preserve">Kota Kendari</t>
+        </is>
+      </c>
+      <c r="D217" s="66">
+        <v>43.65</v>
+      </c>
+      <c r="E217" s="66">
+        <v>17.44</v>
+      </c>
+      <c r="F217" s="66">
+        <v>16.78</v>
+      </c>
+      <c r="G217" s="66">
+        <v>17.25</v>
+      </c>
+      <c r="H217" s="66">
+        <v>1.54</v>
+      </c>
+      <c r="I217" s="66">
+        <v>0.72</v>
+      </c>
+      <c r="J217" s="66">
+        <v>1.06</v>
+      </c>
+      <c r="K217" s="66">
+        <v>1.16</v>
+      </c>
+      <c r="L217" s="66">
+        <v>0.40</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B218">
+        <is>
+          <t xml:space="preserve">Gorontalo</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C218">
+        <is>
+          <t xml:space="preserve">Kota Gorontalo</t>
+        </is>
+      </c>
+      <c r="D218" s="66">
+        <v>21.00</v>
+      </c>
+      <c r="E218" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="F218" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="G218" s="66">
+        <v>30.00</v>
+      </c>
+      <c r="H218" s="66">
+        <v>8.00</v>
+      </c>
+      <c r="I218" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="J218" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="K218" s="66">
+        <v>9.00</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B219">
+        <is>
+          <t xml:space="preserve">Sulawesi Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C219">
+        <is>
+          <t xml:space="preserve">Kab. Majene</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B220">
+        <is>
+          <t xml:space="preserve">Sulawesi Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C220">
+        <is>
+          <t xml:space="preserve">Kab. Mamuju Tengah</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B221">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C221">
+        <is>
+          <t xml:space="preserve">Kab. Maluku Tengah</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B222">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C222">
+        <is>
+          <t xml:space="preserve">Kab. Buru Selatan</t>
+        </is>
+      </c>
+      <c r="D222" s="66">
+        <v>33.00</v>
+      </c>
+      <c r="E222" s="66">
+        <v>22.00</v>
+      </c>
+      <c r="F222" s="66">
+        <v>11.00</v>
+      </c>
+      <c r="G222" s="66">
+        <v>23.00</v>
+      </c>
+      <c r="H222" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="I222" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="J222" s="66">
+        <v>1.00</v>
+      </c>
+      <c r="K222" s="66">
+        <v>2.00</v>
+      </c>
+      <c r="L222" s="66">
+        <v>5.00</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B223">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C223">
+        <is>
+          <t xml:space="preserve">Kota Tual</t>
+        </is>
+      </c>
+      <c r="D223" s="66">
+        <v>8.50</v>
+      </c>
+      <c r="E223" s="66">
+        <v>17.50</v>
+      </c>
+      <c r="F223" s="66">
+        <v>10.80</v>
+      </c>
+      <c r="G223" s="66">
+        <v>15.80</v>
+      </c>
+      <c r="H223" s="66">
+        <v>5.60</v>
+      </c>
+      <c r="I223" s="66">
+        <v>9.30</v>
+      </c>
+      <c r="J223" s="66">
+        <v>7.00</v>
+      </c>
+      <c r="K223" s="66">
+        <v>6.70</v>
+      </c>
+      <c r="L223" s="66">
+        <v>18.80</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B224">
+        <is>
+          <t xml:space="preserve">Maluku Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C224">
+        <is>
+          <t xml:space="preserve">Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="D224" s="66">
+        <v>34.00</v>
+      </c>
+      <c r="E224" s="66">
+        <v>25.00</v>
+      </c>
+      <c r="F224" s="66">
+        <v>12.00</v>
+      </c>
+      <c r="G224" s="66">
+        <v>11.80</v>
+      </c>
+      <c r="H224" s="66">
+        <v>2.30</v>
+      </c>
+      <c r="I224" s="66">
+        <v>0.80</v>
+      </c>
+      <c r="J224" s="66">
+        <v>1.50</v>
+      </c>
+      <c r="K224" s="66">
+        <v>5.80</v>
+      </c>
+      <c r="L224" s="66">
+        <v>6.80</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B225">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C225">
+        <is>
+          <t xml:space="preserve">Kab. Jayapura</t>
+        </is>
+      </c>
+      <c r="D225" s="66">
+        <v>40.00</v>
+      </c>
+      <c r="F225" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="G225" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="H225" s="66">
+        <v>3.00</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B226">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C226">
+        <is>
+          <t xml:space="preserve">Kab. Biak Numfor</t>
+        </is>
+      </c>
+      <c r="D226" s="66">
+        <v>12.88</v>
+      </c>
+      <c r="E226" s="66">
+        <v>39.22</v>
+      </c>
+      <c r="F226" s="66">
+        <v>22.35</v>
+      </c>
+      <c r="G226" s="66">
+        <v>11.63</v>
+      </c>
+      <c r="H226" s="66">
+        <v>10.46</v>
+      </c>
+      <c r="I226" s="66">
+        <v>0.01</v>
+      </c>
+      <c r="J226" s="66">
+        <v>0.13</v>
+      </c>
+      <c r="K226" s="66">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B227">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C227">
+        <is>
+          <t xml:space="preserve">Kab. Keerom</t>
+        </is>
+      </c>
+      <c r="D227" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="E227" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="F227" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="G227" s="66">
+        <v>45.00</v>
+      </c>
+      <c r="H227" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="I227" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="J227" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="K227" s="66">
+        <v>5.00</v>
+      </c>
+      <c r="L227" s="66">
+        <v>5.00</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B228">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C228">
+        <is>
+          <t xml:space="preserve">Kota Jayapura</t>
+        </is>
+      </c>
+      <c r="D228" s="66">
+        <v>67.39</v>
+      </c>
+      <c r="E228" s="66">
+        <v>10.50</v>
+      </c>
+      <c r="F228" s="66">
+        <v>4.78</v>
+      </c>
+      <c r="G228" s="66">
+        <v>6.59</v>
+      </c>
+      <c r="H228" s="66">
+        <v>4.22</v>
+      </c>
+      <c r="I228" s="66">
+        <v>2.04</v>
+      </c>
+      <c r="J228" s="66">
+        <v>1.09</v>
+      </c>
+      <c r="K228" s="66">
+        <v>0.45</v>
+      </c>
+      <c r="L228" s="66">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B229">
+        <is>
+          <t xml:space="preserve">Papua Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C229">
+        <is>
+          <t xml:space="preserve">Kab. Manokwari</t>
+        </is>
+      </c>
+      <c r="D229" s="66">
+        <v>44.00</v>
+      </c>
+      <c r="F229" s="66">
+        <v>11.00</v>
+      </c>
+      <c r="G229" s="66">
+        <v>26.00</v>
+      </c>
+      <c r="L229" s="66">
+        <v>19.00</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B230">
+        <is>
+          <t xml:space="preserve">Papua Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C230">
+        <is>
+          <t xml:space="preserve">Kab. Asmat</t>
+        </is>
+      </c>
+      <c r="D230" s="66">
+        <v>20.00</v>
+      </c>
+      <c r="E230" s="66">
+        <v>10.00</v>
+      </c>
+      <c r="F230" s="66">
+        <v>15.00</v>
+      </c>
+      <c r="G230" s="66">
+        <v>40.00</v>
+      </c>
+      <c r="H230" s="66">
+        <v>4.00</v>
+      </c>
+      <c r="I230" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="J230" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="K230" s="66">
+        <v>3.00</v>
+      </c>
+      <c r="L230" s="66">
+        <v>2.00</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B231">
+        <is>
+          <t xml:space="preserve">Papua Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C231">
+        <is>
+          <t xml:space="preserve">Kab. Nabire</t>
+        </is>
+      </c>
+      <c r="D231" s="66">
+        <v>62.56</v>
+      </c>
+      <c r="E231" s="66">
+        <v>15.13</v>
+      </c>
+      <c r="F231" s="66">
+        <v>4.60</v>
+      </c>
+      <c r="G231" s="66">
+        <v>11.32</v>
+      </c>
+      <c r="H231" s="66">
+        <v>0.48</v>
+      </c>
+      <c r="I231" s="66">
+        <v>1.95</v>
+      </c>
+      <c r="K231" s="66">
+        <v>1.79</v>
+      </c>
+      <c r="L231" s="66">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B232">
+        <is>
+          <t xml:space="preserve">Papua Pegunungan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C232">
+        <is>
+          <t xml:space="preserve">Kab. Lanny Jaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B233">
+        <is>
+          <t xml:space="preserve">Papua Barat Daya</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C233">
+        <is>
+          <t xml:space="preserve">Kab. Sorong Selatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="65">
+        <v>2021</v>
+      </c>
+      <c t="inlineStr" r="B234">
+        <is>
+          <t xml:space="preserve">Papua Barat Daya</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C234">
+        <is>
+          <t xml:space="preserve">Kab. Tambrauw</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
